--- a/output/16_대성_매입단가_제시.xlsx
+++ b/output/16_대성_매입단가_제시.xlsx
@@ -8,12 +8,12 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="매입단가_제시(초안)" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="제시단가_상세내역" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요청단가_상세내역" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="전체493종_매입단가_제시" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'매입단가_제시(초안)'!$A$1:$B$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'제시단가_상세내역'!$A$1:$I$6</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요청단가_상세내역'!$A$1:$J$43</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'전체493종_매입단가_제시'!$A$1:$I$494</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,7 +490,7 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="1" max="1"/>
     <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -514,7 +514,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>대성인포텍에 보낼 이메일/메신저 본문 초안. '제시단가_상세내역'과 '전체493종_매입단가_제시' 시트를 첨부하거나 표를 붙여넣으면 된다.</t>
+          <t>대성인포텍에 보낼 이메일/메신저 본문 초안. '요청단가_상세내역'과 '전체493종_매입단가_제시' 시트를 첨부하거나 표를 붙여넣으면 된다.</t>
         </is>
       </c>
     </row>
@@ -527,17 +527,21 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>안녕하세요, KT commerce 이돈현입니다.
-귀사 8GHz/11GHz 구성 단가표를 검토한 결과, 아래 5개 품목은 매입단가를 다음과 같이 적용하여 진행하고자 합니다.
-1) SFP 3종
-현재 제시된 단가는 할인율 1.0% 수준이나, 귀사 단가표 내 동일 SFP 계열 16개 품목 중 13개(81%)에는 표준 할인율 14.69%가 적용되어 있습니다. 이번 3개 품목에도 동일한 표준 할인율을 적용한 아래 단가로 매입하겠습니다.
-  - CER_1G SFP 1310nm 10km, SMF(K9197304): 22,368원 (정가 26,220원)
-  - CER_10G SFP+ SR 850nm 300m, MMF(K9197306): 36,743원 (정가 43,070원)
-  - CER_2.5G SFP  1310nm 2km, SMF(K9197309): 39,942원 (정가 46,820원)
-2) RFUC-CPLR-8, RFUC-TWIST Kit-6
-두 품목 모두 할인 후 단가가 정가보다 높게(634,418원, 두 품목 동일값) 기재되어 있어 표기 오류로 판단됩니다. 동일 정가를 가진 형제 품목의 실제 적용 단가를 기준으로 아래와 같이 매입단가를 적용하겠습니다.
+귀사 8GHz/11GHz 구성 단가표를 검토한 결과, 아래 42개 품목은 매입단가를 다음과 같이 적용하여 진행하고자 합니다.
+1) 안테나/마운트류 36개 품목
+현재 귀사 단가표상 할인율은 2.00%입니다. 저희는 이 품목들을 귀사 정가 그대로 고객에게 판매할 계획이며, 그 안에서 저희 통상 마진 3%를 확보하려면 할인율 3% 기준 매입이 필요합니다. (예: CER_ANT-15ft-5-RM-DP(K9197334) 17,281,153원 -&gt; 17,104,815원)
+품목별 상세는 첨부 '요청단가_상세내역' 시트를 참고 부탁드립니다.
+2) SFP 3개 품목
+현재 귀사 단가표상 할인율은 1.00%입니다. 저희는 이 품목들을 귀사 정가 그대로 고객에게 판매할 계획이며, 그 안에서 저희 통상 마진 5%를 확보하려면 할인율 5% 기준 매입이 필요합니다. (예: CER_2.5G SFP  1310nm 2km, SMF(K9197309) 46,352원 -&gt; 44,479원)
+품목별 상세는 첨부 '요청단가_상세내역' 시트를 참고 부탁드립니다.
+3) 기타 핵심장비 1개 품목
+현재 귀사 단가표상 할인율은 1.04%입니다. 저희는 이 품목들을 귀사 정가 그대로 고객에게 판매할 계획이며, 그 안에서 저희 통상 마진 2%를 확보하려면 할인율 2% 기준 매입이 필요합니다. (예: CER_32T-WG STRT-11-(400)(K9178690) 204,872원 -&gt; 202,880원)
+품목별 상세는 첨부 '요청단가_상세내역' 시트를 참고 부탁드립니다.
+4) RFUC-CPLR-8, RFUC-TWIST Kit-6
+두 품목 모두 할인 후 단가가 정가보다 높게(634,418원, 두 품목 동일값) 기재되어 있어 표기 오류로 판단됩니다. 정가가 동일한 형제 품목의 실제 적용 단가를 기준으로 아래와 같이 매입단가를 적용하겠습니다.
   - CER_RFUC-CPLR-8(K9178851): 467,968원 (정가 548,550원)
   - CER_RFUC-TWIST Kit-6(K9178856): 105,110원 (정가 123,210원)
-위 5개 품목을 반영한 전체 493개 품목 매입단가 목록을 첨부(전체493종_매입단가_제시 시트)합니다. 나머지 488개 품목은 귀사가 제시하신 단가를 그대로 적용합니다.
+위 품목을 반영한 전체 493개 품목 매입단가 목록을 첨부(전체493종_매입단가_제시 시트)합니다. 나머지 품목은 귀사가 제시하신 단가를 그대로 적용합니다.
 이견 있으시면 회신 부탁드리며, 별도 회신 없을 시 위 단가로 진행하겠습니다.
 감사합니다.</t>
         </is>
@@ -546,12 +550,12 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>참고(내부용, 대성에 보내지 않음)</t>
+          <t>근거 설계(내부용, 대성에 보내지 않음)</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>당초 검토 대상은 21개(안테나/마운트류 17개 포함)였으나, 그 17개는 대성 단가표 내 동일 안테나 계열 41개 품목 전부와 정확히 같은 2.00% 할인율로 이미 일관되어 있음을 확인해 제외함. 15번 파일의 '정가상한 적용 42건'에 이 17개가 걸린 이유는 대성 할인율이 낮아서가 아니라 KT 자체 마진율(안테나 3%)이 대성 할인율(2%)보다 높기 때문 - 이는 대성에 요청할 사안이 아니라 KT 내부 마진 결정의 문제.</t>
+          <t>대성 자체 할인율이 정상/비정상인지는 따지지 않는다(안테나 2%는 대성 단가표 내 41개 동일 계열 전부와 일치하는 정상값). 대신 'KT는 정가 그대로 고객에게 판매하고, 그 안에서 통상 마진율을 남기려면 이 가격에 매입해야 한다'는 KT 자체 마진구조 논리로만 요청한다. 안테나 36개는 2%-&gt;3%로 1%p만 올려달라는 요청이라 현실적이고, SFP는 1%-&gt;5%(4%p)로 이전 버전의 1%-&gt;14.69%(13.69%p) 요청보다 훨씬 작다.</t>
         </is>
       </c>
     </row>
@@ -579,18 +583,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I6"/>
+  <dimension ref="A1:J43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
-    <col width="8" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="22" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
-    <col width="20" customWidth="1" min="8" max="8"/>
-    <col width="55" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="35" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1">
@@ -601,40 +606,45 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
+          <t>마진분류</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
           <t>K코드</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>품명</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>정가</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>대성 현재 제시단가</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>대성 현재 할인율</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>KT 제시 매입단가</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>차액(현재-제시)</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>근거</t>
         </is>
@@ -643,190 +653,1769 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>표준율미적용</t>
+          <t>마진확보</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>K9197304</t>
+          <t>⑪ SFP/광트랜시버</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">CER_1G SFP 1310nm 10km, SMF  </t>
-        </is>
-      </c>
-      <c r="D2" s="4" t="n">
-        <v>26220</v>
+          <t>K9197309</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>CER_2.5G SFP  1310nm 2km, SMF</t>
+        </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>25957.8</v>
-      </c>
-      <c r="F2" s="5" t="n">
-        <v>0.01000000000000003</v>
-      </c>
-      <c r="G2" s="6" t="n">
-        <v>22368</v>
-      </c>
-      <c r="H2" s="4" t="n">
-        <v>3589.799999999999</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>동일 SFP 계열 16종 중 13종(81%)에 적용된 표준 할인율 14.69% 기준 매입단가 제시</t>
+        <v>46820</v>
+      </c>
+      <c r="F2" s="4" t="n">
+        <v>46351.8</v>
+      </c>
+      <c r="G2" s="5" t="n">
+        <v>0.009999999999999898</v>
+      </c>
+      <c r="H2" s="6" t="n">
+        <v>44479</v>
+      </c>
+      <c r="I2" s="4" t="n">
+        <v>1872.800000000003</v>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>표준율미적용</t>
+          <t>마진확보</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
+          <t>⑪ SFP/광트랜시버</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
           <t>K9197306</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">CER_10G SFP+ SR 850nm 300m, MMF </t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>CER_10G SFP+ SR 850nm 300m, MMF</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="n">
         <v>43070</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="F3" s="4" t="n">
         <v>42639.3</v>
       </c>
-      <c r="F3" s="5" t="n">
-        <v>0.009999999999999933</v>
-      </c>
-      <c r="G3" s="6" t="n">
-        <v>36743</v>
-      </c>
-      <c r="H3" s="4" t="n">
-        <v>5896.300000000003</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>동일 SFP 계열 16종 중 13종(81%)에 적용된 표준 할인율 14.69% 기준 매입단가 제시</t>
+      <c r="G3" s="5" t="n">
+        <v>0.009999999999999898</v>
+      </c>
+      <c r="H3" s="6" t="n">
+        <v>40916</v>
+      </c>
+      <c r="I3" s="4" t="n">
+        <v>1722.800000000003</v>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>표준율미적용</t>
+          <t>마진확보</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>K9197309</t>
+          <t>⑪ SFP/광트랜시버</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>CER_2.5G SFP  1310nm 2km, SMF</t>
-        </is>
-      </c>
-      <c r="D4" s="4" t="n">
-        <v>46820</v>
+          <t>K9197304</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>CER_1G SFP 1310nm 10km, SMF</t>
+        </is>
       </c>
       <c r="E4" s="4" t="n">
-        <v>46351.8</v>
-      </c>
-      <c r="F4" s="5" t="n">
-        <v>0.009999999999999938</v>
-      </c>
-      <c r="G4" s="6" t="n">
-        <v>39942</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>6409.800000000003</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>동일 SFP 계열 16종 중 13종(81%)에 적용된 표준 할인율 14.69% 기준 매입단가 제시</t>
+        <v>26220</v>
+      </c>
+      <c r="F4" s="4" t="n">
+        <v>25957.8</v>
+      </c>
+      <c r="G4" s="5" t="n">
+        <v>0.01000000000000001</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>24909</v>
+      </c>
+      <c r="I4" s="4" t="n">
+        <v>1048.799999999999</v>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr">
+      <c r="A5" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>K9197334</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-15ft-5-RM-DP</t>
+        </is>
+      </c>
+      <c r="E5" s="4" t="n">
+        <v>17633830</v>
+      </c>
+      <c r="F5" s="4" t="n">
+        <v>17281153.4</v>
+      </c>
+      <c r="G5" s="5" t="n">
+        <v>0.02000000000000013</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>17104815</v>
+      </c>
+      <c r="I5" s="4" t="n">
+        <v>176338.3000000007</v>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>K9178824</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-15ft-11</t>
+        </is>
+      </c>
+      <c r="E6" s="4" t="n">
+        <v>14163130</v>
+      </c>
+      <c r="F6" s="4" t="n">
+        <v>13879867.4</v>
+      </c>
+      <c r="G6" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="I6" s="4" t="n">
+        <v>141631.3000000007</v>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>K9178823</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-15ft-8</t>
+        </is>
+      </c>
+      <c r="E7" s="4" t="n">
+        <v>14163130</v>
+      </c>
+      <c r="F7" s="4" t="n">
+        <v>13879867.4</v>
+      </c>
+      <c r="G7" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="I7" s="4" t="n">
+        <v>141631.3000000007</v>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>K9178822</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-15ft-6H</t>
+        </is>
+      </c>
+      <c r="E8" s="4" t="n">
+        <v>14163130</v>
+      </c>
+      <c r="F8" s="4" t="n">
+        <v>13879867.4</v>
+      </c>
+      <c r="G8" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>141631.3000000007</v>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>K9178821</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-15ft-6L</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="n">
+        <v>14163130</v>
+      </c>
+      <c r="F9" s="4" t="n">
+        <v>13879867.4</v>
+      </c>
+      <c r="G9" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>141631.3000000007</v>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>K9197333</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-12ft-5-RM-DP</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="n">
+        <v>13804820</v>
+      </c>
+      <c r="F10" s="4" t="n">
+        <v>13528723.6</v>
+      </c>
+      <c r="G10" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>13390675</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>138048.1999999993</v>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>K9197167</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-10ft-5-RM-DP</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="n">
+        <v>11774430</v>
+      </c>
+      <c r="F11" s="4" t="n">
+        <v>11538941.4</v>
+      </c>
+      <c r="G11" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>11421197</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>117744.3000000007</v>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>K9178820</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-12ft-11</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="n">
+        <v>10927020</v>
+      </c>
+      <c r="F12" s="4" t="n">
+        <v>10708479.6</v>
+      </c>
+      <c r="G12" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>109270.1999999993</v>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>K9178819</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-12ft-8</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="n">
+        <v>10927020</v>
+      </c>
+      <c r="F13" s="4" t="n">
+        <v>10708479.6</v>
+      </c>
+      <c r="G13" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>109270.1999999993</v>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>K9178818</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-12ft-6H</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="n">
+        <v>10927020</v>
+      </c>
+      <c r="F14" s="4" t="n">
+        <v>10708479.6</v>
+      </c>
+      <c r="G14" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>109270.1999999993</v>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>K9178817</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-12ft-6L</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="n">
+        <v>10927020</v>
+      </c>
+      <c r="F15" s="4" t="n">
+        <v>10708479.6</v>
+      </c>
+      <c r="G15" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>109270.1999999993</v>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>K9197332</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-8ft-5-RM-DP</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="n">
+        <v>8738110</v>
+      </c>
+      <c r="F16" s="4" t="n">
+        <v>8563347.800000001</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>8475967</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>87381.10000000149</v>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>K9178816</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-10ft-11</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="n">
+        <v>8631560</v>
+      </c>
+      <c r="F17" s="4" t="n">
+        <v>8458928.800000001</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>86315.60000000056</v>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>K9178815</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-10ft-8</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="n">
+        <v>8631560</v>
+      </c>
+      <c r="F18" s="4" t="n">
+        <v>8458928.800000001</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>86315.60000000056</v>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>K9178814</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-10ft-6H</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="n">
+        <v>8631560</v>
+      </c>
+      <c r="F19" s="4" t="n">
+        <v>8458928.800000001</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H19" s="6" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>86315.60000000056</v>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>K9178813</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-10ft-6L</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="n">
+        <v>8631560</v>
+      </c>
+      <c r="F20" s="4" t="n">
+        <v>8458928.800000001</v>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H20" s="6" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="I20" s="4" t="n">
+        <v>86315.60000000056</v>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>K9197331</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-6ft-5-RM-DP</t>
+        </is>
+      </c>
+      <c r="E21" s="4" t="n">
+        <v>7187030</v>
+      </c>
+      <c r="F21" s="4" t="n">
+        <v>7043289.4</v>
+      </c>
+      <c r="G21" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H21" s="6" t="n">
+        <v>6971419</v>
+      </c>
+      <c r="I21" s="4" t="n">
+        <v>71870.30000000075</v>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>K9178812</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-8ft-11</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="n">
+        <v>6542350</v>
+      </c>
+      <c r="F22" s="4" t="n">
+        <v>6411503</v>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H22" s="6" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="I22" s="4" t="n">
+        <v>65423.5</v>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>K9178811</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-8ft-8</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="n">
+        <v>6542350</v>
+      </c>
+      <c r="F23" s="4" t="n">
+        <v>6411503</v>
+      </c>
+      <c r="G23" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H23" s="6" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="I23" s="4" t="n">
+        <v>65423.5</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>K9178810</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-8ft-6H</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="n">
+        <v>6542350</v>
+      </c>
+      <c r="F24" s="4" t="n">
+        <v>6411503</v>
+      </c>
+      <c r="G24" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H24" s="6" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="I24" s="4" t="n">
+        <v>65423.5</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>K9178809</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-8ft-6L</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="n">
+        <v>6542350</v>
+      </c>
+      <c r="F25" s="4" t="n">
+        <v>6411503</v>
+      </c>
+      <c r="G25" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H25" s="6" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="I25" s="4" t="n">
+        <v>65423.5</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>K9178830</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFUC-DM-ANT-HP-SP-6ft-11</t>
+        </is>
+      </c>
+      <c r="E26" s="4" t="n">
+        <v>5343190</v>
+      </c>
+      <c r="F26" s="4" t="n">
+        <v>5236326.2</v>
+      </c>
+      <c r="G26" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H26" s="6" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="I26" s="4" t="n">
+        <v>53431.90000000037</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>K9178829</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFUC-DM-ANT-HP-SP-6ft-8</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="n">
+        <v>5343190</v>
+      </c>
+      <c r="F27" s="4" t="n">
+        <v>5236326.2</v>
+      </c>
+      <c r="G27" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H27" s="6" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="I27" s="4" t="n">
+        <v>53431.90000000037</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>K9178828</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFUC-DM-ANT-HP-SP-6ft-6H</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="n">
+        <v>5343190</v>
+      </c>
+      <c r="F28" s="4" t="n">
+        <v>5236326.2</v>
+      </c>
+      <c r="G28" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H28" s="6" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="I28" s="4" t="n">
+        <v>53431.90000000037</v>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>K9178878</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFUC-DM-ANT-HP-SP-6ft-6L</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="n">
+        <v>5343190</v>
+      </c>
+      <c r="F29" s="4" t="n">
+        <v>5236326.2</v>
+      </c>
+      <c r="G29" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H29" s="6" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="I29" s="4" t="n">
+        <v>53431.90000000037</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>K9178808</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-6ft-11</t>
+        </is>
+      </c>
+      <c r="E30" s="4" t="n">
+        <v>4919190</v>
+      </c>
+      <c r="F30" s="4" t="n">
+        <v>4820806.2</v>
+      </c>
+      <c r="G30" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H30" s="6" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="I30" s="4" t="n">
+        <v>49191.90000000037</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>K9178807</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-6ft-8</t>
+        </is>
+      </c>
+      <c r="E31" s="4" t="n">
+        <v>4919190</v>
+      </c>
+      <c r="F31" s="4" t="n">
+        <v>4820806.2</v>
+      </c>
+      <c r="G31" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H31" s="6" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="I31" s="4" t="n">
+        <v>49191.90000000037</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>K9178806</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-6ft-6H</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="n">
+        <v>4919190</v>
+      </c>
+      <c r="F32" s="4" t="n">
+        <v>4820806.2</v>
+      </c>
+      <c r="G32" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H32" s="6" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="I32" s="4" t="n">
+        <v>49191.90000000037</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>K9178805</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-6ft-6L</t>
+        </is>
+      </c>
+      <c r="E33" s="4" t="n">
+        <v>4919190</v>
+      </c>
+      <c r="F33" s="4" t="n">
+        <v>4820806.2</v>
+      </c>
+      <c r="G33" s="5" t="n">
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="H33" s="6" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="I33" s="4" t="n">
+        <v>49191.90000000037</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>K9178804</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-4ft-11</t>
+        </is>
+      </c>
+      <c r="E34" s="4" t="n">
+        <v>3494770</v>
+      </c>
+      <c r="F34" s="4" t="n">
+        <v>3424874.6</v>
+      </c>
+      <c r="G34" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H34" s="6" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="I34" s="4" t="n">
+        <v>34947.70000000019</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>K9178803</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-4ft-8</t>
+        </is>
+      </c>
+      <c r="E35" s="4" t="n">
+        <v>3494770</v>
+      </c>
+      <c r="F35" s="4" t="n">
+        <v>3424874.6</v>
+      </c>
+      <c r="G35" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H35" s="6" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="I35" s="4" t="n">
+        <v>34947.70000000019</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>K9178802</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-4ft-6H</t>
+        </is>
+      </c>
+      <c r="E36" s="4" t="n">
+        <v>3494770</v>
+      </c>
+      <c r="F36" s="4" t="n">
+        <v>3424874.6</v>
+      </c>
+      <c r="G36" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H36" s="6" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="I36" s="4" t="n">
+        <v>34947.70000000019</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>K9178800</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>CER_ANT-HP-DP-4ft-6L</t>
+        </is>
+      </c>
+      <c r="E37" s="4" t="n">
+        <v>3494770</v>
+      </c>
+      <c r="F37" s="4" t="n">
+        <v>3424874.6</v>
+      </c>
+      <c r="G37" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H37" s="6" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="I37" s="4" t="n">
+        <v>34947.70000000019</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>K9178877</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFUC-DM-ANT-HP-SP-4ft-11</t>
+        </is>
+      </c>
+      <c r="E38" s="4" t="n">
+        <v>3024380</v>
+      </c>
+      <c r="F38" s="4" t="n">
+        <v>2963892.4</v>
+      </c>
+      <c r="G38" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H38" s="6" t="n">
+        <v>2933649</v>
+      </c>
+      <c r="I38" s="4" t="n">
+        <v>30243.79999999981</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>K9178876</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFUC-DM-ANT-HP-SP-4ft-8</t>
+        </is>
+      </c>
+      <c r="E39" s="4" t="n">
+        <v>3024380</v>
+      </c>
+      <c r="F39" s="4" t="n">
+        <v>2963892.4</v>
+      </c>
+      <c r="G39" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H39" s="6" t="n">
+        <v>2933649</v>
+      </c>
+      <c r="I39" s="4" t="n">
+        <v>30243.79999999981</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>안테나/마운트/방수(패턴)</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>K9178875</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFUC-DM-ANT-HP-SP-4ft-6H</t>
+        </is>
+      </c>
+      <c r="E40" s="4" t="n">
+        <v>3024380</v>
+      </c>
+      <c r="F40" s="4" t="n">
+        <v>2963892.4</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="H40" s="6" t="n">
+        <v>2933649</v>
+      </c>
+      <c r="I40" s="4" t="n">
+        <v>30243.79999999981</v>
+      </c>
+      <c r="J40" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="3" t="inlineStr">
+        <is>
+          <t>마진확보</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>핵심장비(패턴, 기본값)</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>K9178690</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>CER_32T-WG STRT-11-(400)</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="n">
+        <v>207020</v>
+      </c>
+      <c r="F41" s="4" t="n">
+        <v>204872</v>
+      </c>
+      <c r="G41" s="5" t="n">
+        <v>0.01037580910057001</v>
+      </c>
+      <c r="H41" s="6" t="n">
+        <v>202880</v>
+      </c>
+      <c r="I41" s="4" t="n">
+        <v>1992.399999999994</v>
+      </c>
+      <c r="J41" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 2%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="7" t="inlineStr">
         <is>
           <t>표기오류</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
         <is>
           <t>K9178851</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CER_RFUC-CPLR-8</t>
-        </is>
-      </c>
-      <c r="D5" s="4" t="n">
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFUC-CPLR-8</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="n">
         <v>548550</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="F42" s="4" t="n">
         <v>634418</v>
       </c>
-      <c r="F5" s="8" t="n">
+      <c r="G42" s="8" t="n">
         <v>-0.1565363230334518</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="H42" s="9" t="n">
         <v>467968.005</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="I42" s="4" t="n">
         <v>166449.995</v>
       </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>정가가 동일한 형제 품목 CER_RFUC-CPLR-6(K9178850)의 실제 적용 단가를 기준으로 제시 (표준 할인율 0.8531 적용값과도 일치)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="7" t="inlineStr">
+      <c r="J42" s="2" t="inlineStr">
+        <is>
+          <t>정가가 동일한 형제 품목 CER_RFUC-CPLR-6(K9178850)의 실제 적용 단가를 기준으로 제시</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="7" t="inlineStr">
         <is>
           <t>표기오류</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
         <is>
           <t>K9178856</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve"> CER_RFUC-TWIST Kit-6</t>
-        </is>
-      </c>
-      <c r="D6" s="4" t="n">
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>CER_RFUC-TWIST Kit-6</t>
+        </is>
+      </c>
+      <c r="E43" s="4" t="n">
         <v>123210</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="F43" s="4" t="n">
         <v>634418</v>
       </c>
-      <c r="F6" s="8" t="n">
+      <c r="G43" s="8" t="n">
         <v>-4.149078808538268</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="H43" s="9" t="n">
         <v>105110.451</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="I43" s="4" t="n">
         <v>529307.549</v>
       </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>정가가 동일한 형제 품목 CER_RFUC-TWIST Kit-8(K9178857)의 실제 적용 단가를 기준으로 제시 (표준 할인율 0.8531 적용값과도 일치)</t>
+      <c r="J43" s="2" t="inlineStr">
+        <is>
+          <t>정가가 동일한 형제 품목 CER_RFUC-TWIST Kit-8(K9178857)의 실제 적용 단가를 기준으로 제시</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I6"/>
+  <autoFilter ref="A1:J43"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2181,17 +3770,21 @@
         <v>204872</v>
       </c>
       <c r="F38" s="5" t="n">
-        <v>0.01037580910056999</v>
-      </c>
-      <c r="G38" s="4" t="n">
-        <v>204872</v>
-      </c>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr"/>
+        <v>0.01037580910057001</v>
+      </c>
+      <c r="G38" s="6" t="n">
+        <v>202880</v>
+      </c>
+      <c r="H38" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 2%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -4176,17 +5769,21 @@
         <v>3424874.6</v>
       </c>
       <c r="F95" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G95" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="H95" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G95" s="6" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="H95" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -4211,17 +5808,21 @@
         <v>3424874.6</v>
       </c>
       <c r="F96" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G96" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="H96" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G96" s="6" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="H96" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -4246,17 +5847,21 @@
         <v>3424874.6</v>
       </c>
       <c r="F97" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G97" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="H97" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G97" s="6" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="H97" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -4281,17 +5886,21 @@
         <v>3424874.6</v>
       </c>
       <c r="F98" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G98" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="H98" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G98" s="6" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="H98" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -4316,17 +5925,21 @@
         <v>4820806.2</v>
       </c>
       <c r="F99" s="5" t="n">
-        <v>0.01999999999999996</v>
-      </c>
-      <c r="G99" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="H99" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr"/>
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="G99" s="6" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="H99" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -4351,17 +5964,21 @@
         <v>4820806.2</v>
       </c>
       <c r="F100" s="5" t="n">
-        <v>0.01999999999999996</v>
-      </c>
-      <c r="G100" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="H100" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr"/>
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="G100" s="6" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="H100" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -4386,17 +6003,21 @@
         <v>4820806.2</v>
       </c>
       <c r="F101" s="5" t="n">
-        <v>0.01999999999999996</v>
-      </c>
-      <c r="G101" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="H101" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr"/>
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="G101" s="6" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="H101" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -4421,17 +6042,21 @@
         <v>4820806.2</v>
       </c>
       <c r="F102" s="5" t="n">
-        <v>0.01999999999999996</v>
-      </c>
-      <c r="G102" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="H102" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr"/>
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="G102" s="6" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="H102" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -4456,17 +6081,21 @@
         <v>6411503</v>
       </c>
       <c r="F103" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G103" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="H103" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G103" s="6" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="H103" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -4491,17 +6120,21 @@
         <v>6411503</v>
       </c>
       <c r="F104" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G104" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="H104" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G104" s="6" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="H104" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -4526,17 +6159,21 @@
         <v>6411503</v>
       </c>
       <c r="F105" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G105" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="H105" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G105" s="6" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="H105" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -4561,17 +6198,21 @@
         <v>6411503</v>
       </c>
       <c r="F106" s="5" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="G106" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="H106" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G106" s="6" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="H106" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -4598,15 +6239,19 @@
       <c r="F107" s="5" t="n">
         <v>0.01999999999999991</v>
       </c>
-      <c r="G107" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="H107" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr"/>
+      <c r="G107" s="6" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="H107" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -4633,15 +6278,19 @@
       <c r="F108" s="5" t="n">
         <v>0.01999999999999991</v>
       </c>
-      <c r="G108" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="H108" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr"/>
+      <c r="G108" s="6" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="H108" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -4668,15 +6317,19 @@
       <c r="F109" s="5" t="n">
         <v>0.01999999999999991</v>
       </c>
-      <c r="G109" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="H109" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr"/>
+      <c r="G109" s="6" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="H109" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -4703,15 +6356,19 @@
       <c r="F110" s="5" t="n">
         <v>0.01999999999999991</v>
       </c>
-      <c r="G110" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="H110" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr"/>
+      <c r="G110" s="6" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="H110" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -4736,17 +6393,21 @@
         <v>10708479.6</v>
       </c>
       <c r="F111" s="5" t="n">
-        <v>0.02000000000000004</v>
-      </c>
-      <c r="G111" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="H111" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G111" s="6" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="H111" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -4771,17 +6432,21 @@
         <v>10708479.6</v>
       </c>
       <c r="F112" s="5" t="n">
-        <v>0.02000000000000004</v>
-      </c>
-      <c r="G112" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="H112" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G112" s="6" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="H112" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -4806,17 +6471,21 @@
         <v>10708479.6</v>
       </c>
       <c r="F113" s="5" t="n">
-        <v>0.02000000000000004</v>
-      </c>
-      <c r="G113" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="H113" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G113" s="6" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="H113" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -4841,17 +6510,21 @@
         <v>10708479.6</v>
       </c>
       <c r="F114" s="5" t="n">
-        <v>0.02000000000000004</v>
-      </c>
-      <c r="G114" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="H114" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G114" s="6" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="H114" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -4876,17 +6549,21 @@
         <v>13879867.4</v>
       </c>
       <c r="F115" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G115" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="H115" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G115" s="6" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="H115" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -4911,17 +6588,21 @@
         <v>13879867.4</v>
       </c>
       <c r="F116" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G116" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="H116" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G116" s="6" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="H116" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -4946,17 +6627,21 @@
         <v>13879867.4</v>
       </c>
       <c r="F117" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G117" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="H117" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G117" s="6" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="H117" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -4981,17 +6666,21 @@
         <v>13879867.4</v>
       </c>
       <c r="F118" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G118" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="H118" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G118" s="6" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="H118" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -5121,17 +6810,21 @@
         <v>5236326.2</v>
       </c>
       <c r="F122" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G122" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="H122" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G122" s="6" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="H122" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -5156,17 +6849,21 @@
         <v>5236326.2</v>
       </c>
       <c r="F123" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G123" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="H123" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G123" s="6" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="H123" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -5191,17 +6888,21 @@
         <v>5236326.2</v>
       </c>
       <c r="F124" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G124" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="H124" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G124" s="6" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="H124" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -5933,12 +7634,12 @@
       </c>
       <c r="H145" s="3" t="inlineStr">
         <is>
-          <t>수정 제시</t>
+          <t>표기오류 수정 제시</t>
         </is>
       </c>
       <c r="I145" s="2" t="inlineStr">
         <is>
-          <t>정가가 동일한 형제 품목 CER_RFUC-CPLR-6(K9178850)의 실제 적용 단가를 기준으로 제시 (표준 할인율 0.8531 적용값과도 일치)</t>
+          <t>정가가 동일한 형제 품목 CER_RFUC-CPLR-6(K9178850)의 실제 적용 단가를 기준으로 제시</t>
         </is>
       </c>
     </row>
@@ -6007,12 +7708,12 @@
       </c>
       <c r="H147" s="3" t="inlineStr">
         <is>
-          <t>수정 제시</t>
+          <t>표기오류 수정 제시</t>
         </is>
       </c>
       <c r="I147" s="2" t="inlineStr">
         <is>
-          <t>정가가 동일한 형제 품목 CER_RFUC-TWIST Kit-8(K9178857)의 실제 적용 단가를 기준으로 제시 (표준 할인율 0.8531 적용값과도 일치)</t>
+          <t>정가가 동일한 형제 품목 CER_RFUC-TWIST Kit-8(K9178857)의 실제 적용 단가를 기준으로 제시</t>
         </is>
       </c>
     </row>
@@ -6669,17 +8370,21 @@
         <v>2963892.4</v>
       </c>
       <c r="F166" s="5" t="n">
-        <v>0.02000000000000003</v>
-      </c>
-      <c r="G166" s="4" t="n">
-        <v>2963892.4</v>
-      </c>
-      <c r="H166" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G166" s="6" t="n">
+        <v>2933649</v>
+      </c>
+      <c r="H166" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -6704,17 +8409,21 @@
         <v>2963892.4</v>
       </c>
       <c r="F167" s="5" t="n">
-        <v>0.02000000000000003</v>
-      </c>
-      <c r="G167" s="4" t="n">
-        <v>2963892.4</v>
-      </c>
-      <c r="H167" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G167" s="6" t="n">
+        <v>2933649</v>
+      </c>
+      <c r="H167" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -6739,17 +8448,21 @@
         <v>2963892.4</v>
       </c>
       <c r="F168" s="5" t="n">
-        <v>0.02000000000000003</v>
-      </c>
-      <c r="G168" s="4" t="n">
-        <v>2963892.4</v>
-      </c>
-      <c r="H168" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G168" s="6" t="n">
+        <v>2933649</v>
+      </c>
+      <c r="H168" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -6774,17 +8487,21 @@
         <v>5236326.2</v>
       </c>
       <c r="F169" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G169" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="H169" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G169" s="6" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="H169" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -11429,17 +13146,21 @@
         <v>11538941.4</v>
       </c>
       <c r="F302" s="5" t="n">
-        <v>0.01999999999999997</v>
-      </c>
-      <c r="G302" s="4" t="n">
-        <v>11538941.4</v>
-      </c>
-      <c r="H302" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I302" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G302" s="6" t="n">
+        <v>11421197</v>
+      </c>
+      <c r="H302" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -15384,19 +17105,19 @@
         <v>25957.8</v>
       </c>
       <c r="F415" s="5" t="n">
-        <v>0.01000000000000003</v>
+        <v>0.01000000000000001</v>
       </c>
       <c r="G415" s="6" t="n">
-        <v>22368</v>
+        <v>24909</v>
       </c>
       <c r="H415" s="3" t="inlineStr">
         <is>
-          <t>수정 제시</t>
+          <t>마진 확보 위한 수정 제시</t>
         </is>
       </c>
       <c r="I415" s="2" t="inlineStr">
         <is>
-          <t>동일 SFP 계열 16종 중 13종(81%)에 적용된 표준 할인율 14.69% 기준 매입단가 제시</t>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
         </is>
       </c>
     </row>
@@ -15458,19 +17179,19 @@
         <v>42639.3</v>
       </c>
       <c r="F417" s="5" t="n">
-        <v>0.009999999999999933</v>
+        <v>0.009999999999999898</v>
       </c>
       <c r="G417" s="6" t="n">
-        <v>36743</v>
+        <v>40916</v>
       </c>
       <c r="H417" s="3" t="inlineStr">
         <is>
-          <t>수정 제시</t>
+          <t>마진 확보 위한 수정 제시</t>
         </is>
       </c>
       <c r="I417" s="2" t="inlineStr">
         <is>
-          <t>동일 SFP 계열 16종 중 13종(81%)에 적용된 표준 할인율 14.69% 기준 매입단가 제시</t>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
         </is>
       </c>
     </row>
@@ -15567,19 +17288,19 @@
         <v>46351.8</v>
       </c>
       <c r="F420" s="5" t="n">
-        <v>0.009999999999999938</v>
+        <v>0.009999999999999898</v>
       </c>
       <c r="G420" s="6" t="n">
-        <v>39942</v>
+        <v>44479</v>
       </c>
       <c r="H420" s="3" t="inlineStr">
         <is>
-          <t>수정 제시</t>
+          <t>마진 확보 위한 수정 제시</t>
         </is>
       </c>
       <c r="I420" s="2" t="inlineStr">
         <is>
-          <t>동일 SFP 계열 16종 중 13종(81%)에 적용된 표준 할인율 14.69% 기준 매입단가 제시</t>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
         </is>
       </c>
     </row>
@@ -16341,17 +18062,21 @@
         <v>7043289.4</v>
       </c>
       <c r="F442" s="5" t="n">
-        <v>0.01999999999999995</v>
-      </c>
-      <c r="G442" s="4" t="n">
-        <v>7043289.4</v>
-      </c>
-      <c r="H442" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I442" s="2" t="inlineStr"/>
+        <v>0.01999999999999991</v>
+      </c>
+      <c r="G442" s="6" t="n">
+        <v>6971419</v>
+      </c>
+      <c r="H442" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -16378,15 +18103,19 @@
       <c r="F443" s="5" t="n">
         <v>0.01999999999999991</v>
       </c>
-      <c r="G443" s="4" t="n">
-        <v>8563347.800000001</v>
-      </c>
-      <c r="H443" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I443" s="2" t="inlineStr"/>
+      <c r="G443" s="6" t="n">
+        <v>8475967</v>
+      </c>
+      <c r="H443" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -16411,17 +18140,21 @@
         <v>13528723.6</v>
       </c>
       <c r="F444" s="5" t="n">
-        <v>0.02000000000000003</v>
-      </c>
-      <c r="G444" s="4" t="n">
-        <v>13528723.6</v>
-      </c>
-      <c r="H444" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I444" s="2" t="inlineStr"/>
+        <v>0.02000000000000002</v>
+      </c>
+      <c r="G444" s="6" t="n">
+        <v>13390675</v>
+      </c>
+      <c r="H444" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -16446,17 +18179,21 @@
         <v>17281153.4</v>
       </c>
       <c r="F445" s="5" t="n">
-        <v>0.02000000000000008</v>
-      </c>
-      <c r="G445" s="4" t="n">
-        <v>17281153.4</v>
-      </c>
-      <c r="H445" s="2" t="inlineStr">
-        <is>
-          <t>대성 제시가 수용</t>
-        </is>
-      </c>
-      <c r="I445" s="2" t="inlineStr"/>
+        <v>0.02000000000000013</v>
+      </c>
+      <c r="G445" s="6" t="n">
+        <v>17104815</v>
+      </c>
+      <c r="H445" s="3" t="inlineStr">
+        <is>
+          <t>마진 확보 위한 수정 제시</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr">
+        <is>
+          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
+        </is>
+      </c>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">

--- a/output/16_대성_매입단가_제시.xlsx
+++ b/output/16_대성_매입단가_제시.xlsx
@@ -13,7 +13,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'매입단가_제시(초안)'!$A$1:$B$5</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요청단가_상세내역'!$A$1:$J$43</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'요청단가_상세내역'!$A$1:$J$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'전체493종_매입단가_제시'!$A$1:$I$494</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -53,17 +53,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFE699"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="00FFC7CE"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
   </fills>
@@ -93,7 +93,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -107,19 +107,16 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -527,16 +524,7 @@
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>안녕하세요, KT commerce 이돈현입니다.
-귀사 8GHz/11GHz 구성 단가표를 검토한 결과, 아래 42개 품목은 매입단가를 다음과 같이 적용하여 진행하고자 합니다.
-1) 안테나/마운트류 36개 품목
-현재 귀사 단가표상 할인율은 2.00%입니다. 저희는 이 품목들을 귀사 정가 그대로 고객에게 판매할 계획이며, 그 안에서 저희 통상 마진 3%를 확보하려면 할인율 3% 기준 매입이 필요합니다. (예: CER_ANT-15ft-5-RM-DP(K9197334) 17,281,153원 -&gt; 17,104,815원)
-품목별 상세는 첨부 '요청단가_상세내역' 시트를 참고 부탁드립니다.
-2) SFP 3개 품목
-현재 귀사 단가표상 할인율은 1.00%입니다. 저희는 이 품목들을 귀사 정가 그대로 고객에게 판매할 계획이며, 그 안에서 저희 통상 마진 5%를 확보하려면 할인율 5% 기준 매입이 필요합니다. (예: CER_2.5G SFP  1310nm 2km, SMF(K9197309) 46,352원 -&gt; 44,479원)
-품목별 상세는 첨부 '요청단가_상세내역' 시트를 참고 부탁드립니다.
-3) 기타 핵심장비 1개 품목
-현재 귀사 단가표상 할인율은 1.04%입니다. 저희는 이 품목들을 귀사 정가 그대로 고객에게 판매할 계획이며, 그 안에서 저희 통상 마진 2%를 확보하려면 할인율 2% 기준 매입이 필요합니다. (예: CER_32T-WG STRT-11-(400)(K9178690) 204,872원 -&gt; 202,880원)
-품목별 상세는 첨부 '요청단가_상세내역' 시트를 참고 부탁드립니다.
+귀사 8GHz/11GHz 구성 단가표를 검토한 결과, 아래 2개 품목은 매입단가를 다음과 같이 적용하여 진행하고자 합니다.
 4) RFUC-CPLR-8, RFUC-TWIST Kit-6
 두 품목 모두 할인 후 단가가 정가보다 높게(634,418원, 두 품목 동일값) 기재되어 있어 표기 오류로 판단됩니다. 정가가 동일한 형제 품목의 실제 적용 단가를 기준으로 아래와 같이 매입단가를 적용하겠습니다.
   - CER_RFUC-CPLR-8(K9178851): 467,968원 (정가 548,550원)
@@ -583,18 +571,18 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J43"/>
+  <dimension ref="A1:J3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="8" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="35" customWidth="1" min="4" max="4"/>
-    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
     <col width="12" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="21" customWidth="1" min="7" max="7"/>
     <col width="12" customWidth="1" min="8" max="8"/>
-    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="9" max="9"/>
     <col width="55" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
@@ -653,1769 +641,89 @@
     <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>마진확보</t>
+          <t>표기오류</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>⑪ SFP/광트랜시버</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
-          <t>K9197309</t>
+          <t>K9178851</t>
         </is>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>CER_2.5G SFP  1310nm 2km, SMF</t>
+          <t>CER_RFUC-CPLR-8</t>
         </is>
       </c>
       <c r="E2" s="4" t="n">
-        <v>46820</v>
+        <v>548550</v>
       </c>
       <c r="F2" s="4" t="n">
-        <v>46351.8</v>
+        <v>467968</v>
       </c>
       <c r="G2" s="5" t="n">
-        <v>0.009999999999999898</v>
+        <v>0.1469000091149394</v>
       </c>
       <c r="H2" s="6" t="n">
-        <v>44479</v>
+        <v>467968.005</v>
       </c>
       <c r="I2" s="4" t="n">
-        <v>1872.800000000003</v>
+        <v>-0.005000000004656613</v>
       </c>
       <c r="J2" s="2" t="inlineStr">
         <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
+          <t>정가가 동일한 형제 품목 CER_RFUC-CPLR-6(K9178850)의 실제 적용 단가를 기준으로 제시</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>마진확보</t>
+          <t>표기오류</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>⑪ SFP/광트랜시버</t>
+          <t>-</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>K9197306</t>
+          <t>K9178856</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>CER_10G SFP+ SR 850nm 300m, MMF</t>
+          <t>CER_RFUC-TWIST Kit-6</t>
         </is>
       </c>
       <c r="E3" s="4" t="n">
-        <v>43070</v>
+        <v>123210</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>42639.3</v>
+        <v>105110</v>
       </c>
       <c r="G3" s="5" t="n">
-        <v>0.009999999999999898</v>
+        <v>0.1469036604171739</v>
       </c>
       <c r="H3" s="6" t="n">
-        <v>40916</v>
+        <v>105110.451</v>
       </c>
       <c r="I3" s="4" t="n">
-        <v>1722.800000000003</v>
+        <v>-0.4510000000009313</v>
       </c>
       <c r="J3" s="2" t="inlineStr">
         <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>⑪ SFP/광트랜시버</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>K9197304</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>CER_1G SFP 1310nm 10km, SMF</t>
-        </is>
-      </c>
-      <c r="E4" s="4" t="n">
-        <v>26220</v>
-      </c>
-      <c r="F4" s="4" t="n">
-        <v>25957.8</v>
-      </c>
-      <c r="G4" s="5" t="n">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="H4" s="6" t="n">
-        <v>24909</v>
-      </c>
-      <c r="I4" s="4" t="n">
-        <v>1048.799999999999</v>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>K9197334</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-15ft-5-RM-DP</t>
-        </is>
-      </c>
-      <c r="E5" s="4" t="n">
-        <v>17633830</v>
-      </c>
-      <c r="F5" s="4" t="n">
-        <v>17281153.4</v>
-      </c>
-      <c r="G5" s="5" t="n">
-        <v>0.02000000000000013</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>17104815</v>
-      </c>
-      <c r="I5" s="4" t="n">
-        <v>176338.3000000007</v>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>K9178824</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-15ft-11</t>
-        </is>
-      </c>
-      <c r="E6" s="4" t="n">
-        <v>14163130</v>
-      </c>
-      <c r="F6" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="G6" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H6" s="6" t="n">
-        <v>13738236</v>
-      </c>
-      <c r="I6" s="4" t="n">
-        <v>141631.3000000007</v>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>K9178823</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-15ft-8</t>
-        </is>
-      </c>
-      <c r="E7" s="4" t="n">
-        <v>14163130</v>
-      </c>
-      <c r="F7" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="G7" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>13738236</v>
-      </c>
-      <c r="I7" s="4" t="n">
-        <v>141631.3000000007</v>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>K9178822</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-15ft-6H</t>
-        </is>
-      </c>
-      <c r="E8" s="4" t="n">
-        <v>14163130</v>
-      </c>
-      <c r="F8" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="G8" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H8" s="6" t="n">
-        <v>13738236</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>141631.3000000007</v>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>K9178821</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-15ft-6L</t>
-        </is>
-      </c>
-      <c r="E9" s="4" t="n">
-        <v>14163130</v>
-      </c>
-      <c r="F9" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="G9" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>13738236</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>141631.3000000007</v>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>K9197333</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-12ft-5-RM-DP</t>
-        </is>
-      </c>
-      <c r="E10" s="4" t="n">
-        <v>13804820</v>
-      </c>
-      <c r="F10" s="4" t="n">
-        <v>13528723.6</v>
-      </c>
-      <c r="G10" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>13390675</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>138048.1999999993</v>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>K9197167</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-10ft-5-RM-DP</t>
-        </is>
-      </c>
-      <c r="E11" s="4" t="n">
-        <v>11774430</v>
-      </c>
-      <c r="F11" s="4" t="n">
-        <v>11538941.4</v>
-      </c>
-      <c r="G11" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H11" s="6" t="n">
-        <v>11421197</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>117744.3000000007</v>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>K9178820</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-12ft-11</t>
-        </is>
-      </c>
-      <c r="E12" s="4" t="n">
-        <v>10927020</v>
-      </c>
-      <c r="F12" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="G12" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H12" s="6" t="n">
-        <v>10599209</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>109270.1999999993</v>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>K9178819</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-12ft-8</t>
-        </is>
-      </c>
-      <c r="E13" s="4" t="n">
-        <v>10927020</v>
-      </c>
-      <c r="F13" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="G13" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H13" s="6" t="n">
-        <v>10599209</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>109270.1999999993</v>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>K9178818</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-12ft-6H</t>
-        </is>
-      </c>
-      <c r="E14" s="4" t="n">
-        <v>10927020</v>
-      </c>
-      <c r="F14" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="G14" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H14" s="6" t="n">
-        <v>10599209</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>109270.1999999993</v>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>K9178817</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-12ft-6L</t>
-        </is>
-      </c>
-      <c r="E15" s="4" t="n">
-        <v>10927020</v>
-      </c>
-      <c r="F15" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="G15" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H15" s="6" t="n">
-        <v>10599209</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>109270.1999999993</v>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>K9197332</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-8ft-5-RM-DP</t>
-        </is>
-      </c>
-      <c r="E16" s="4" t="n">
-        <v>8738110</v>
-      </c>
-      <c r="F16" s="4" t="n">
-        <v>8563347.800000001</v>
-      </c>
-      <c r="G16" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H16" s="6" t="n">
-        <v>8475967</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>87381.10000000149</v>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>K9178816</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-10ft-11</t>
-        </is>
-      </c>
-      <c r="E17" s="4" t="n">
-        <v>8631560</v>
-      </c>
-      <c r="F17" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="G17" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H17" s="6" t="n">
-        <v>8372613</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>86315.60000000056</v>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>K9178815</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-10ft-8</t>
-        </is>
-      </c>
-      <c r="E18" s="4" t="n">
-        <v>8631560</v>
-      </c>
-      <c r="F18" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="G18" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H18" s="6" t="n">
-        <v>8372613</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>86315.60000000056</v>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>K9178814</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-10ft-6H</t>
-        </is>
-      </c>
-      <c r="E19" s="4" t="n">
-        <v>8631560</v>
-      </c>
-      <c r="F19" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="G19" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H19" s="6" t="n">
-        <v>8372613</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>86315.60000000056</v>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>K9178813</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-10ft-6L</t>
-        </is>
-      </c>
-      <c r="E20" s="4" t="n">
-        <v>8631560</v>
-      </c>
-      <c r="F20" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="G20" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H20" s="6" t="n">
-        <v>8372613</v>
-      </c>
-      <c r="I20" s="4" t="n">
-        <v>86315.60000000056</v>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>K9197331</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-6ft-5-RM-DP</t>
-        </is>
-      </c>
-      <c r="E21" s="4" t="n">
-        <v>7187030</v>
-      </c>
-      <c r="F21" s="4" t="n">
-        <v>7043289.4</v>
-      </c>
-      <c r="G21" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H21" s="6" t="n">
-        <v>6971419</v>
-      </c>
-      <c r="I21" s="4" t="n">
-        <v>71870.30000000075</v>
-      </c>
-      <c r="J21" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>K9178812</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-8ft-11</t>
-        </is>
-      </c>
-      <c r="E22" s="4" t="n">
-        <v>6542350</v>
-      </c>
-      <c r="F22" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="G22" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H22" s="6" t="n">
-        <v>6346080</v>
-      </c>
-      <c r="I22" s="4" t="n">
-        <v>65423.5</v>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>K9178811</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-8ft-8</t>
-        </is>
-      </c>
-      <c r="E23" s="4" t="n">
-        <v>6542350</v>
-      </c>
-      <c r="F23" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="G23" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H23" s="6" t="n">
-        <v>6346080</v>
-      </c>
-      <c r="I23" s="4" t="n">
-        <v>65423.5</v>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>K9178810</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-8ft-6H</t>
-        </is>
-      </c>
-      <c r="E24" s="4" t="n">
-        <v>6542350</v>
-      </c>
-      <c r="F24" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="G24" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H24" s="6" t="n">
-        <v>6346080</v>
-      </c>
-      <c r="I24" s="4" t="n">
-        <v>65423.5</v>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>K9178809</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-8ft-6L</t>
-        </is>
-      </c>
-      <c r="E25" s="4" t="n">
-        <v>6542350</v>
-      </c>
-      <c r="F25" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="G25" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H25" s="6" t="n">
-        <v>6346080</v>
-      </c>
-      <c r="I25" s="4" t="n">
-        <v>65423.5</v>
-      </c>
-      <c r="J25" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>K9178830</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>CER_RFUC-DM-ANT-HP-SP-6ft-11</t>
-        </is>
-      </c>
-      <c r="E26" s="4" t="n">
-        <v>5343190</v>
-      </c>
-      <c r="F26" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="G26" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H26" s="6" t="n">
-        <v>5182894</v>
-      </c>
-      <c r="I26" s="4" t="n">
-        <v>53431.90000000037</v>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>K9178829</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>CER_RFUC-DM-ANT-HP-SP-6ft-8</t>
-        </is>
-      </c>
-      <c r="E27" s="4" t="n">
-        <v>5343190</v>
-      </c>
-      <c r="F27" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="G27" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H27" s="6" t="n">
-        <v>5182894</v>
-      </c>
-      <c r="I27" s="4" t="n">
-        <v>53431.90000000037</v>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>K9178828</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>CER_RFUC-DM-ANT-HP-SP-6ft-6H</t>
-        </is>
-      </c>
-      <c r="E28" s="4" t="n">
-        <v>5343190</v>
-      </c>
-      <c r="F28" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="G28" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H28" s="6" t="n">
-        <v>5182894</v>
-      </c>
-      <c r="I28" s="4" t="n">
-        <v>53431.90000000037</v>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B29" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>K9178878</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>CER_RFUC-DM-ANT-HP-SP-6ft-6L</t>
-        </is>
-      </c>
-      <c r="E29" s="4" t="n">
-        <v>5343190</v>
-      </c>
-      <c r="F29" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="G29" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H29" s="6" t="n">
-        <v>5182894</v>
-      </c>
-      <c r="I29" s="4" t="n">
-        <v>53431.90000000037</v>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>K9178808</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-6ft-11</t>
-        </is>
-      </c>
-      <c r="E30" s="4" t="n">
-        <v>4919190</v>
-      </c>
-      <c r="F30" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="G30" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H30" s="6" t="n">
-        <v>4771614</v>
-      </c>
-      <c r="I30" s="4" t="n">
-        <v>49191.90000000037</v>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>K9178807</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-6ft-8</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="n">
-        <v>4919190</v>
-      </c>
-      <c r="F31" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="G31" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H31" s="6" t="n">
-        <v>4771614</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>49191.90000000037</v>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B32" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>K9178806</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-6ft-6H</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="n">
-        <v>4919190</v>
-      </c>
-      <c r="F32" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="G32" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H32" s="6" t="n">
-        <v>4771614</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>49191.90000000037</v>
-      </c>
-      <c r="J32" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B33" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>K9178805</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-6ft-6L</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="n">
-        <v>4919190</v>
-      </c>
-      <c r="F33" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="G33" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="H33" s="6" t="n">
-        <v>4771614</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>49191.90000000037</v>
-      </c>
-      <c r="J33" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B34" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>K9178804</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-4ft-11</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="n">
-        <v>3494770</v>
-      </c>
-      <c r="F34" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H34" s="6" t="n">
-        <v>3389927</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>34947.70000000019</v>
-      </c>
-      <c r="J34" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B35" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>K9178803</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-4ft-8</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="n">
-        <v>3494770</v>
-      </c>
-      <c r="F35" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="G35" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H35" s="6" t="n">
-        <v>3389927</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>34947.70000000019</v>
-      </c>
-      <c r="J35" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>K9178802</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-4ft-6H</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="n">
-        <v>3494770</v>
-      </c>
-      <c r="F36" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="G36" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H36" s="6" t="n">
-        <v>3389927</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>34947.70000000019</v>
-      </c>
-      <c r="J36" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>K9178800</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>CER_ANT-HP-DP-4ft-6L</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="n">
-        <v>3494770</v>
-      </c>
-      <c r="F37" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="G37" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H37" s="6" t="n">
-        <v>3389927</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>34947.70000000019</v>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>K9178877</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>CER_RFUC-DM-ANT-HP-SP-4ft-11</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="n">
-        <v>3024380</v>
-      </c>
-      <c r="F38" s="4" t="n">
-        <v>2963892.4</v>
-      </c>
-      <c r="G38" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H38" s="6" t="n">
-        <v>2933649</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>30243.79999999981</v>
-      </c>
-      <c r="J38" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>K9178876</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
-        <is>
-          <t>CER_RFUC-DM-ANT-HP-SP-4ft-8</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="n">
-        <v>3024380</v>
-      </c>
-      <c r="F39" s="4" t="n">
-        <v>2963892.4</v>
-      </c>
-      <c r="G39" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H39" s="6" t="n">
-        <v>2933649</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>30243.79999999981</v>
-      </c>
-      <c r="J39" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>안테나/마운트/방수(패턴)</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>K9178875</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
-        <is>
-          <t>CER_RFUC-DM-ANT-HP-SP-4ft-6H</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="n">
-        <v>3024380</v>
-      </c>
-      <c r="F40" s="4" t="n">
-        <v>2963892.4</v>
-      </c>
-      <c r="G40" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="H40" s="6" t="n">
-        <v>2933649</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>30243.79999999981</v>
-      </c>
-      <c r="J40" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="3" t="inlineStr">
-        <is>
-          <t>마진확보</t>
-        </is>
-      </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>핵심장비(패턴, 기본값)</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>K9178690</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
-        <is>
-          <t>CER_32T-WG STRT-11-(400)</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="n">
-        <v>207020</v>
-      </c>
-      <c r="F41" s="4" t="n">
-        <v>204872</v>
-      </c>
-      <c r="G41" s="5" t="n">
-        <v>0.01037580910057001</v>
-      </c>
-      <c r="H41" s="6" t="n">
-        <v>202880</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>1992.399999999994</v>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 2%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="7" t="inlineStr">
-        <is>
-          <t>표기오류</t>
-        </is>
-      </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>K9178851</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
-        <is>
-          <t>CER_RFUC-CPLR-8</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="n">
-        <v>548550</v>
-      </c>
-      <c r="F42" s="4" t="n">
-        <v>634418</v>
-      </c>
-      <c r="G42" s="8" t="n">
-        <v>-0.1565363230334518</v>
-      </c>
-      <c r="H42" s="9" t="n">
-        <v>467968.005</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>166449.995</v>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>정가가 동일한 형제 품목 CER_RFUC-CPLR-6(K9178850)의 실제 적용 단가를 기준으로 제시</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="7" t="inlineStr">
-        <is>
-          <t>표기오류</t>
-        </is>
-      </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>K9178856</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
-        <is>
-          <t>CER_RFUC-TWIST Kit-6</t>
-        </is>
-      </c>
-      <c r="E43" s="4" t="n">
-        <v>123210</v>
-      </c>
-      <c r="F43" s="4" t="n">
-        <v>634418</v>
-      </c>
-      <c r="G43" s="8" t="n">
-        <v>-4.149078808538268</v>
-      </c>
-      <c r="H43" s="9" t="n">
-        <v>105110.451</v>
-      </c>
-      <c r="I43" s="4" t="n">
-        <v>529307.549</v>
-      </c>
-      <c r="J43" s="2" t="inlineStr">
-        <is>
           <t>정가가 동일한 형제 품목 CER_RFUC-TWIST Kit-8(K9178857)의 실제 적용 단가를 기준으로 제시</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J43"/>
+  <autoFilter ref="A1:J3"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -2509,7 +817,7 @@
       <c r="E2" s="4" t="n">
         <v>485558.927</v>
       </c>
-      <c r="F2" s="5" t="n">
+      <c r="F2" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G2" s="4" t="n">
@@ -2544,7 +852,7 @@
       <c r="E3" s="4" t="n">
         <v>284636.815</v>
       </c>
-      <c r="F3" s="5" t="n">
+      <c r="F3" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G3" s="4" t="n">
@@ -2579,7 +887,7 @@
       <c r="E4" s="4" t="n">
         <v>284636.815</v>
       </c>
-      <c r="F4" s="5" t="n">
+      <c r="F4" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G4" s="4" t="n">
@@ -2614,7 +922,7 @@
       <c r="E5" s="4" t="n">
         <v>267890.462</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="F5" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G5" s="4" t="n">
@@ -2649,7 +957,7 @@
       <c r="E6" s="4" t="n">
         <v>13547.228</v>
       </c>
-      <c r="F6" s="5" t="n">
+      <c r="F6" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G6" s="4" t="n">
@@ -2684,7 +992,7 @@
       <c r="E7" s="4" t="n">
         <v>339107.25</v>
       </c>
-      <c r="F7" s="5" t="n">
+      <c r="F7" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G7" s="4" t="n">
@@ -2719,7 +1027,7 @@
       <c r="E8" s="4" t="n">
         <v>251144.109</v>
       </c>
-      <c r="F8" s="5" t="n">
+      <c r="F8" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G8" s="4" t="n">
@@ -2754,7 +1062,7 @@
       <c r="E9" s="4" t="n">
         <v>237375.075</v>
       </c>
-      <c r="F9" s="5" t="n">
+      <c r="F9" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G9" s="4" t="n">
@@ -2789,7 +1097,7 @@
       <c r="E10" s="4" t="n">
         <v>379518.597</v>
       </c>
-      <c r="F10" s="5" t="n">
+      <c r="F10" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G10" s="4" t="n">
@@ -2824,7 +1132,7 @@
       <c r="E11" s="4" t="n">
         <v>379518.597</v>
       </c>
-      <c r="F11" s="5" t="n">
+      <c r="F11" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G11" s="4" t="n">
@@ -2859,7 +1167,7 @@
       <c r="E12" s="4" t="n">
         <v>357192.97</v>
       </c>
-      <c r="F12" s="5" t="n">
+      <c r="F12" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G12" s="4" t="n">
@@ -2894,7 +1202,7 @@
       <c r="E13" s="4" t="n">
         <v>329279.538</v>
       </c>
-      <c r="F13" s="5" t="n">
+      <c r="F13" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G13" s="4" t="n">
@@ -2929,7 +1237,7 @@
       <c r="E14" s="4" t="n">
         <v>429749.125</v>
       </c>
-      <c r="F14" s="5" t="n">
+      <c r="F14" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G14" s="4" t="n">
@@ -2964,7 +1272,7 @@
       <c r="E15" s="4" t="n">
         <v>429749.125</v>
       </c>
-      <c r="F15" s="5" t="n">
+      <c r="F15" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G15" s="4" t="n">
@@ -2999,7 +1307,7 @@
       <c r="E16" s="4" t="n">
         <v>407423.498</v>
       </c>
-      <c r="F16" s="5" t="n">
+      <c r="F16" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G16" s="4" t="n">
@@ -3034,7 +1342,7 @@
       <c r="E17" s="4" t="n">
         <v>379518.597</v>
       </c>
-      <c r="F17" s="5" t="n">
+      <c r="F17" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G17" s="4" t="n">
@@ -3069,7 +1377,7 @@
       <c r="E18" s="4" t="n">
         <v>597187.062</v>
       </c>
-      <c r="F18" s="5" t="n">
+      <c r="F18" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G18" s="4" t="n">
@@ -3104,7 +1412,7 @@
       <c r="E19" s="4" t="n">
         <v>597187.062</v>
       </c>
-      <c r="F19" s="5" t="n">
+      <c r="F19" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G19" s="4" t="n">
@@ -3139,7 +1447,7 @@
       <c r="E20" s="4" t="n">
         <v>558115.0819999999</v>
       </c>
-      <c r="F20" s="5" t="n">
+      <c r="F20" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G20" s="4" t="n">
@@ -3174,7 +1482,7 @@
       <c r="E21" s="4" t="n">
         <v>507884.554</v>
       </c>
-      <c r="F21" s="5" t="n">
+      <c r="F21" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G21" s="4" t="n">
@@ -3209,7 +1517,7 @@
       <c r="E22" s="4" t="n">
         <v>376333</v>
       </c>
-      <c r="F22" s="5" t="n">
+      <c r="F22" s="7" t="n">
         <v>0.2529369727047147</v>
       </c>
       <c r="G22" s="4" t="n">
@@ -3244,7 +1552,7 @@
       <c r="E23" s="4" t="n">
         <v>376333</v>
       </c>
-      <c r="F23" s="5" t="n">
+      <c r="F23" s="7" t="n">
         <v>0.2529369727047147</v>
       </c>
       <c r="G23" s="4" t="n">
@@ -3279,7 +1587,7 @@
       <c r="E24" s="4" t="n">
         <v>376333.04</v>
       </c>
-      <c r="F24" s="5" t="n">
+      <c r="F24" s="7" t="n">
         <v>0.212</v>
       </c>
       <c r="G24" s="4" t="n">
@@ -3314,7 +1622,7 @@
       <c r="E25" s="4" t="n">
         <v>376333</v>
       </c>
-      <c r="F25" s="5" t="n">
+      <c r="F25" s="7" t="n">
         <v>0.1540607368444714</v>
       </c>
       <c r="G25" s="4" t="n">
@@ -3349,7 +1657,7 @@
       <c r="E26" s="4" t="n">
         <v>44642.723</v>
       </c>
-      <c r="F26" s="5" t="n">
+      <c r="F26" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G26" s="4" t="n">
@@ -3384,7 +1692,7 @@
       <c r="E27" s="4" t="n">
         <v>44642.723</v>
       </c>
-      <c r="F27" s="5" t="n">
+      <c r="F27" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G27" s="4" t="n">
@@ -3419,7 +1727,7 @@
       <c r="E28" s="4" t="n">
         <v>39063.449</v>
       </c>
-      <c r="F28" s="5" t="n">
+      <c r="F28" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G28" s="4" t="n">
@@ -3454,7 +1762,7 @@
       <c r="E29" s="4" t="n">
         <v>542580.1310000001</v>
       </c>
-      <c r="F29" s="5" t="n">
+      <c r="F29" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G29" s="4" t="n">
@@ -3489,7 +1797,7 @@
       <c r="E30" s="4" t="n">
         <v>54240.098</v>
       </c>
-      <c r="F30" s="5" t="n">
+      <c r="F30" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G30" s="4" t="n">
@@ -3524,7 +1832,7 @@
       <c r="E31" s="4" t="n">
         <v>733683.062</v>
       </c>
-      <c r="F31" s="5" t="n">
+      <c r="F31" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G31" s="4" t="n">
@@ -3559,7 +1867,7 @@
       <c r="E32" s="4" t="n">
         <v>217028</v>
       </c>
-      <c r="F32" s="5" t="n">
+      <c r="F32" s="7" t="n">
         <v>0.1908582506897323</v>
       </c>
       <c r="G32" s="4" t="n">
@@ -3594,7 +1902,7 @@
       <c r="E33" s="4" t="n">
         <v>217028</v>
       </c>
-      <c r="F33" s="5" t="n">
+      <c r="F33" s="7" t="n">
         <v>0.1493434719554737</v>
       </c>
       <c r="G33" s="4" t="n">
@@ -3629,7 +1937,7 @@
       <c r="E34" s="4" t="n">
         <v>217027.8</v>
       </c>
-      <c r="F34" s="5" t="n">
+      <c r="F34" s="7" t="n">
         <v>0.1270000000000001</v>
       </c>
       <c r="G34" s="4" t="n">
@@ -3664,7 +1972,7 @@
       <c r="E35" s="4" t="n">
         <v>217028</v>
       </c>
-      <c r="F35" s="5" t="n">
+      <c r="F35" s="7" t="n">
         <v>0.07847649781325634</v>
       </c>
       <c r="G35" s="4" t="n">
@@ -3699,7 +2007,7 @@
       <c r="E36" s="4" t="n">
         <v>204872</v>
       </c>
-      <c r="F36" s="5" t="n">
+      <c r="F36" s="7" t="n">
         <v>0.250294580451568</v>
       </c>
       <c r="G36" s="4" t="n">
@@ -3734,7 +2042,7 @@
       <c r="E37" s="4" t="n">
         <v>204871.965</v>
       </c>
-      <c r="F37" s="5" t="n">
+      <c r="F37" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G37" s="4" t="n">
@@ -3767,24 +2075,20 @@
         <v>207020</v>
       </c>
       <c r="E38" s="4" t="n">
-        <v>204872</v>
-      </c>
-      <c r="F38" s="5" t="n">
-        <v>0.01037580910057001</v>
-      </c>
-      <c r="G38" s="6" t="n">
         <v>202880</v>
       </c>
-      <c r="H38" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 2%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F38" s="7" t="n">
+        <v>0.01999806781953434</v>
+      </c>
+      <c r="G38" s="4" t="n">
+        <v>202880</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -3808,7 +2112,7 @@
       <c r="E39" s="4" t="n">
         <v>176609</v>
       </c>
-      <c r="F39" s="5" t="n">
+      <c r="F39" s="7" t="n">
         <v>0.2383275111053608</v>
       </c>
       <c r="G39" s="4" t="n">
@@ -3843,7 +2147,7 @@
       <c r="E40" s="4" t="n">
         <v>176608.762</v>
       </c>
-      <c r="F40" s="5" t="n">
+      <c r="F40" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G40" s="4" t="n">
@@ -3878,7 +2182,7 @@
       <c r="E41" s="4" t="n">
         <v>176609</v>
       </c>
-      <c r="F41" s="5" t="n">
+      <c r="F41" s="7" t="n">
         <v>0.0727239315341804</v>
       </c>
       <c r="G41" s="4" t="n">
@@ -3913,7 +2217,7 @@
       <c r="E42" s="4" t="n">
         <v>282589</v>
       </c>
-      <c r="F42" s="5" t="n">
+      <c r="F42" s="7" t="n">
         <v>0.2244449323489859</v>
       </c>
       <c r="G42" s="4" t="n">
@@ -3948,7 +2252,7 @@
       <c r="E43" s="4" t="n">
         <v>282589.375</v>
       </c>
-      <c r="F43" s="5" t="n">
+      <c r="F43" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G43" s="4" t="n">
@@ -3983,7 +2287,7 @@
       <c r="E44" s="4" t="n">
         <v>282589</v>
       </c>
-      <c r="F44" s="5" t="n">
+      <c r="F44" s="7" t="n">
         <v>0.05209647121964309</v>
       </c>
       <c r="G44" s="4" t="n">
@@ -4018,7 +2322,7 @@
       <c r="E45" s="4" t="n">
         <v>2590839.107</v>
       </c>
-      <c r="F45" s="5" t="n">
+      <c r="F45" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G45" s="4" t="n">
@@ -4053,7 +2357,7 @@
       <c r="E46" s="4" t="n">
         <v>2590839.107</v>
       </c>
-      <c r="F46" s="5" t="n">
+      <c r="F46" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G46" s="4" t="n">
@@ -4088,7 +2392,7 @@
       <c r="E47" s="4" t="n">
         <v>2590839.107</v>
       </c>
-      <c r="F47" s="5" t="n">
+      <c r="F47" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G47" s="4" t="n">
@@ -4123,7 +2427,7 @@
       <c r="E48" s="4" t="n">
         <v>2590839.107</v>
       </c>
-      <c r="F48" s="5" t="n">
+      <c r="F48" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G48" s="4" t="n">
@@ -4158,7 +2462,7 @@
       <c r="E49" s="4" t="n">
         <v>2590839.107</v>
       </c>
-      <c r="F49" s="5" t="n">
+      <c r="F49" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G49" s="4" t="n">
@@ -4193,7 +2497,7 @@
       <c r="E50" s="4" t="n">
         <v>2590839.107</v>
       </c>
-      <c r="F50" s="5" t="n">
+      <c r="F50" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G50" s="4" t="n">
@@ -4228,7 +2532,7 @@
       <c r="E51" s="4" t="n">
         <v>2957083.468</v>
       </c>
-      <c r="F51" s="5" t="n">
+      <c r="F51" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G51" s="4" t="n">
@@ -4263,7 +2567,7 @@
       <c r="E52" s="4" t="n">
         <v>2957083.468</v>
       </c>
-      <c r="F52" s="5" t="n">
+      <c r="F52" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G52" s="4" t="n">
@@ -4298,7 +2602,7 @@
       <c r="E53" s="4" t="n">
         <v>2896035.632</v>
       </c>
-      <c r="F53" s="5" t="n">
+      <c r="F53" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G53" s="4" t="n">
@@ -4333,7 +2637,7 @@
       <c r="E54" s="4" t="n">
         <v>2896035.632</v>
       </c>
-      <c r="F54" s="5" t="n">
+      <c r="F54" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G54" s="4" t="n">
@@ -4368,7 +2672,7 @@
       <c r="E55" s="4" t="n">
         <v>2896035.632</v>
       </c>
-      <c r="F55" s="5" t="n">
+      <c r="F55" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G55" s="4" t="n">
@@ -4403,7 +2707,7 @@
       <c r="E56" s="4" t="n">
         <v>3208022.833</v>
       </c>
-      <c r="F56" s="5" t="n">
+      <c r="F56" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G56" s="4" t="n">
@@ -4438,7 +2742,7 @@
       <c r="E57" s="4" t="n">
         <v>651094.451</v>
       </c>
-      <c r="F57" s="5" t="n">
+      <c r="F57" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G57" s="4" t="n">
@@ -4473,7 +2777,7 @@
       <c r="E58" s="4" t="n">
         <v>651094.451</v>
       </c>
-      <c r="F58" s="5" t="n">
+      <c r="F58" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G58" s="4" t="n">
@@ -4508,7 +2812,7 @@
       <c r="E59" s="4" t="n">
         <v>651094.451</v>
       </c>
-      <c r="F59" s="5" t="n">
+      <c r="F59" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G59" s="4" t="n">
@@ -4543,7 +2847,7 @@
       <c r="E60" s="4" t="n">
         <v>651094.451</v>
       </c>
-      <c r="F60" s="5" t="n">
+      <c r="F60" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G60" s="4" t="n">
@@ -4578,7 +2882,7 @@
       <c r="E61" s="4" t="n">
         <v>651094.451</v>
       </c>
-      <c r="F61" s="5" t="n">
+      <c r="F61" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G61" s="4" t="n">
@@ -4613,7 +2917,7 @@
       <c r="E62" s="4" t="n">
         <v>651094.451</v>
       </c>
-      <c r="F62" s="5" t="n">
+      <c r="F62" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G62" s="4" t="n">
@@ -4648,7 +2952,7 @@
       <c r="E63" s="4" t="n">
         <v>651094.451</v>
       </c>
-      <c r="F63" s="5" t="n">
+      <c r="F63" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G63" s="4" t="n">
@@ -4683,7 +2987,7 @@
       <c r="E64" s="4" t="n">
         <v>651094.451</v>
       </c>
-      <c r="F64" s="5" t="n">
+      <c r="F64" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G64" s="4" t="n">
@@ -4718,7 +3022,7 @@
       <c r="E65" s="4" t="n">
         <v>922380.2509999999</v>
       </c>
-      <c r="F65" s="5" t="n">
+      <c r="F65" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G65" s="4" t="n">
@@ -4753,7 +3057,7 @@
       <c r="E66" s="4" t="n">
         <v>922380.2509999999</v>
       </c>
-      <c r="F66" s="5" t="n">
+      <c r="F66" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G66" s="4" t="n">
@@ -4788,7 +3092,7 @@
       <c r="E67" s="4" t="n">
         <v>922380.2509999999</v>
       </c>
-      <c r="F67" s="5" t="n">
+      <c r="F67" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G67" s="4" t="n">
@@ -4823,7 +3127,7 @@
       <c r="E68" s="4" t="n">
         <v>922380.2509999999</v>
       </c>
-      <c r="F68" s="5" t="n">
+      <c r="F68" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G68" s="4" t="n">
@@ -4858,7 +3162,7 @@
       <c r="E69" s="4" t="n">
         <v>922380.2509999999</v>
       </c>
-      <c r="F69" s="5" t="n">
+      <c r="F69" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G69" s="4" t="n">
@@ -4893,7 +3197,7 @@
       <c r="E70" s="4" t="n">
         <v>922380.2509999999</v>
       </c>
-      <c r="F70" s="5" t="n">
+      <c r="F70" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G70" s="4" t="n">
@@ -4928,7 +3232,7 @@
       <c r="E71" s="4" t="n">
         <v>922380.2509999999</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F71" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G71" s="4" t="n">
@@ -4963,7 +3267,7 @@
       <c r="E72" s="4" t="n">
         <v>922380.2509999999</v>
       </c>
-      <c r="F72" s="5" t="n">
+      <c r="F72" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G72" s="4" t="n">
@@ -4998,7 +3302,7 @@
       <c r="E73" s="4" t="n">
         <v>162762.949</v>
       </c>
-      <c r="F73" s="5" t="n">
+      <c r="F73" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G73" s="4" t="n">
@@ -5033,7 +3337,7 @@
       <c r="E74" s="4" t="n">
         <v>23050.762</v>
       </c>
-      <c r="F74" s="5" t="n">
+      <c r="F74" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G74" s="4" t="n">
@@ -5068,7 +3372,7 @@
       <c r="E75" s="4" t="n">
         <v>23050.762</v>
       </c>
-      <c r="F75" s="5" t="n">
+      <c r="F75" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G75" s="4" t="n">
@@ -5103,7 +3407,7 @@
       <c r="E76" s="4" t="n">
         <v>23050.762</v>
       </c>
-      <c r="F76" s="5" t="n">
+      <c r="F76" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G76" s="4" t="n">
@@ -5138,7 +3442,7 @@
       <c r="E77" s="4" t="n">
         <v>74595.064</v>
       </c>
-      <c r="F77" s="5" t="n">
+      <c r="F77" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G77" s="4" t="n">
@@ -5173,7 +3477,7 @@
       <c r="E78" s="4" t="n">
         <v>74595.064</v>
       </c>
-      <c r="F78" s="5" t="n">
+      <c r="F78" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G78" s="4" t="n">
@@ -5208,7 +3512,7 @@
       <c r="E79" s="4" t="n">
         <v>74595.064</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F79" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G79" s="4" t="n">
@@ -5243,7 +3547,7 @@
       <c r="E80" s="4" t="n">
         <v>58309.385</v>
       </c>
-      <c r="F80" s="5" t="n">
+      <c r="F80" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G80" s="4" t="n">
@@ -5278,7 +3582,7 @@
       <c r="E81" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F81" s="5" t="n">
+      <c r="F81" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G81" s="4" t="n">
@@ -5313,7 +3617,7 @@
       <c r="E82" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F82" s="5" t="n">
+      <c r="F82" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G82" s="4" t="n">
@@ -5348,7 +3652,7 @@
       <c r="E83" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F83" s="5" t="n">
+      <c r="F83" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G83" s="4" t="n">
@@ -5383,7 +3687,7 @@
       <c r="E84" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F84" s="5" t="n">
+      <c r="F84" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G84" s="4" t="n">
@@ -5418,7 +3722,7 @@
       <c r="E85" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F85" s="5" t="n">
+      <c r="F85" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G85" s="4" t="n">
@@ -5453,7 +3757,7 @@
       <c r="E86" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F86" s="5" t="n">
+      <c r="F86" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G86" s="4" t="n">
@@ -5488,7 +3792,7 @@
       <c r="E87" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F87" s="5" t="n">
+      <c r="F87" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G87" s="4" t="n">
@@ -5523,7 +3827,7 @@
       <c r="E88" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F88" s="5" t="n">
+      <c r="F88" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G88" s="4" t="n">
@@ -5558,7 +3862,7 @@
       <c r="E89" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F89" s="5" t="n">
+      <c r="F89" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G89" s="4" t="n">
@@ -5593,7 +3897,7 @@
       <c r="E90" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F90" s="5" t="n">
+      <c r="F90" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G90" s="4" t="n">
@@ -5628,7 +3932,7 @@
       <c r="E91" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F91" s="5" t="n">
+      <c r="F91" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G91" s="4" t="n">
@@ -5663,7 +3967,7 @@
       <c r="E92" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F92" s="5" t="n">
+      <c r="F92" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G92" s="4" t="n">
@@ -5698,7 +4002,7 @@
       <c r="E93" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F93" s="5" t="n">
+      <c r="F93" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G93" s="4" t="n">
@@ -5733,7 +4037,7 @@
       <c r="E94" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F94" s="5" t="n">
+      <c r="F94" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G94" s="4" t="n">
@@ -5766,24 +4070,20 @@
         <v>3494770</v>
       </c>
       <c r="E95" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="F95" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G95" s="6" t="n">
         <v>3389927</v>
       </c>
-      <c r="H95" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I95" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F95" s="7" t="n">
+        <v>0.02999997138581366</v>
+      </c>
+      <c r="G95" s="4" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="H95" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I95" s="2" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="2" t="inlineStr">
@@ -5805,24 +4105,20 @@
         <v>3494770</v>
       </c>
       <c r="E96" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="F96" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G96" s="6" t="n">
         <v>3389927</v>
       </c>
-      <c r="H96" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I96" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F96" s="7" t="n">
+        <v>0.02999997138581366</v>
+      </c>
+      <c r="G96" s="4" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="H96" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I96" s="2" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="2" t="inlineStr">
@@ -5844,24 +4140,20 @@
         <v>3494770</v>
       </c>
       <c r="E97" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="F97" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G97" s="6" t="n">
         <v>3389927</v>
       </c>
-      <c r="H97" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I97" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F97" s="7" t="n">
+        <v>0.02999997138581366</v>
+      </c>
+      <c r="G97" s="4" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="H97" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I97" s="2" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" s="2" t="inlineStr">
@@ -5883,24 +4175,20 @@
         <v>3494770</v>
       </c>
       <c r="E98" s="4" t="n">
-        <v>3424874.6</v>
-      </c>
-      <c r="F98" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G98" s="6" t="n">
         <v>3389927</v>
       </c>
-      <c r="H98" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I98" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F98" s="7" t="n">
+        <v>0.02999997138581366</v>
+      </c>
+      <c r="G98" s="4" t="n">
+        <v>3389927</v>
+      </c>
+      <c r="H98" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I98" s="2" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" s="2" t="inlineStr">
@@ -5922,24 +4210,20 @@
         <v>4919190</v>
       </c>
       <c r="E99" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="F99" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G99" s="6" t="n">
         <v>4771614</v>
       </c>
-      <c r="H99" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I99" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F99" s="7" t="n">
+        <v>0.03000006098565008</v>
+      </c>
+      <c r="G99" s="4" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="H99" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I99" s="2" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" s="2" t="inlineStr">
@@ -5961,24 +4245,20 @@
         <v>4919190</v>
       </c>
       <c r="E100" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="F100" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G100" s="6" t="n">
         <v>4771614</v>
       </c>
-      <c r="H100" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I100" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F100" s="7" t="n">
+        <v>0.03000006098565008</v>
+      </c>
+      <c r="G100" s="4" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="H100" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I100" s="2" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" s="2" t="inlineStr">
@@ -6000,24 +4280,20 @@
         <v>4919190</v>
       </c>
       <c r="E101" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="F101" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G101" s="6" t="n">
         <v>4771614</v>
       </c>
-      <c r="H101" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I101" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F101" s="7" t="n">
+        <v>0.03000006098565008</v>
+      </c>
+      <c r="G101" s="4" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="H101" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I101" s="2" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="2" t="inlineStr">
@@ -6039,24 +4315,20 @@
         <v>4919190</v>
       </c>
       <c r="E102" s="4" t="n">
-        <v>4820806.2</v>
-      </c>
-      <c r="F102" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G102" s="6" t="n">
         <v>4771614</v>
       </c>
-      <c r="H102" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I102" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F102" s="7" t="n">
+        <v>0.03000006098565008</v>
+      </c>
+      <c r="G102" s="4" t="n">
+        <v>4771614</v>
+      </c>
+      <c r="H102" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I102" s="2" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="2" t="inlineStr">
@@ -6078,24 +4350,20 @@
         <v>6542350</v>
       </c>
       <c r="E103" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="F103" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G103" s="6" t="n">
         <v>6346080</v>
       </c>
-      <c r="H103" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I103" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F103" s="7" t="n">
+        <v>0.02999992357486224</v>
+      </c>
+      <c r="G103" s="4" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="H103" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I103" s="2" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" s="2" t="inlineStr">
@@ -6117,24 +4385,20 @@
         <v>6542350</v>
       </c>
       <c r="E104" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="F104" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G104" s="6" t="n">
         <v>6346080</v>
       </c>
-      <c r="H104" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I104" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F104" s="7" t="n">
+        <v>0.02999992357486224</v>
+      </c>
+      <c r="G104" s="4" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="H104" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I104" s="2" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" s="2" t="inlineStr">
@@ -6156,24 +4420,20 @@
         <v>6542350</v>
       </c>
       <c r="E105" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="F105" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G105" s="6" t="n">
         <v>6346080</v>
       </c>
-      <c r="H105" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I105" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F105" s="7" t="n">
+        <v>0.02999992357486224</v>
+      </c>
+      <c r="G105" s="4" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I105" s="2" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" s="2" t="inlineStr">
@@ -6195,24 +4455,20 @@
         <v>6542350</v>
       </c>
       <c r="E106" s="4" t="n">
-        <v>6411503</v>
-      </c>
-      <c r="F106" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G106" s="6" t="n">
         <v>6346080</v>
       </c>
-      <c r="H106" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I106" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F106" s="7" t="n">
+        <v>0.02999992357486224</v>
+      </c>
+      <c r="G106" s="4" t="n">
+        <v>6346080</v>
+      </c>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I106" s="2" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="2" t="inlineStr">
@@ -6234,24 +4490,20 @@
         <v>8631560</v>
       </c>
       <c r="E107" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="F107" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G107" s="6" t="n">
         <v>8372613</v>
       </c>
-      <c r="H107" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I107" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F107" s="7" t="n">
+        <v>0.03000002317078257</v>
+      </c>
+      <c r="G107" s="4" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="H107" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I107" s="2" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="2" t="inlineStr">
@@ -6273,24 +4525,20 @@
         <v>8631560</v>
       </c>
       <c r="E108" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="F108" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G108" s="6" t="n">
         <v>8372613</v>
       </c>
-      <c r="H108" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I108" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F108" s="7" t="n">
+        <v>0.03000002317078257</v>
+      </c>
+      <c r="G108" s="4" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="H108" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I108" s="2" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" s="2" t="inlineStr">
@@ -6312,24 +4560,20 @@
         <v>8631560</v>
       </c>
       <c r="E109" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="F109" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G109" s="6" t="n">
         <v>8372613</v>
       </c>
-      <c r="H109" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I109" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F109" s="7" t="n">
+        <v>0.03000002317078257</v>
+      </c>
+      <c r="G109" s="4" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="H109" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I109" s="2" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" s="2" t="inlineStr">
@@ -6351,24 +4595,20 @@
         <v>8631560</v>
       </c>
       <c r="E110" s="4" t="n">
-        <v>8458928.800000001</v>
-      </c>
-      <c r="F110" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G110" s="6" t="n">
         <v>8372613</v>
       </c>
-      <c r="H110" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I110" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F110" s="7" t="n">
+        <v>0.03000002317078257</v>
+      </c>
+      <c r="G110" s="4" t="n">
+        <v>8372613</v>
+      </c>
+      <c r="H110" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I110" s="2" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" s="2" t="inlineStr">
@@ -6390,24 +4630,20 @@
         <v>10927020</v>
       </c>
       <c r="E111" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="F111" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G111" s="6" t="n">
         <v>10599209</v>
       </c>
-      <c r="H111" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I111" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F111" s="7" t="n">
+        <v>0.03000003660650388</v>
+      </c>
+      <c r="G111" s="4" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="H111" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I111" s="2" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" s="2" t="inlineStr">
@@ -6429,24 +4665,20 @@
         <v>10927020</v>
       </c>
       <c r="E112" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="F112" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G112" s="6" t="n">
         <v>10599209</v>
       </c>
-      <c r="H112" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I112" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F112" s="7" t="n">
+        <v>0.03000003660650388</v>
+      </c>
+      <c r="G112" s="4" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="H112" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I112" s="2" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="2" t="inlineStr">
@@ -6468,24 +4700,20 @@
         <v>10927020</v>
       </c>
       <c r="E113" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="F113" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G113" s="6" t="n">
         <v>10599209</v>
       </c>
-      <c r="H113" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I113" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F113" s="7" t="n">
+        <v>0.03000003660650388</v>
+      </c>
+      <c r="G113" s="4" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="H113" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I113" s="2" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="2" t="inlineStr">
@@ -6507,24 +4735,20 @@
         <v>10927020</v>
       </c>
       <c r="E114" s="4" t="n">
-        <v>10708479.6</v>
-      </c>
-      <c r="F114" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G114" s="6" t="n">
         <v>10599209</v>
       </c>
-      <c r="H114" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I114" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F114" s="7" t="n">
+        <v>0.03000003660650388</v>
+      </c>
+      <c r="G114" s="4" t="n">
+        <v>10599209</v>
+      </c>
+      <c r="H114" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I114" s="2" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" s="2" t="inlineStr">
@@ -6546,24 +4770,20 @@
         <v>14163130</v>
       </c>
       <c r="E115" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="F115" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G115" s="6" t="n">
         <v>13738236</v>
       </c>
-      <c r="H115" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I115" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F115" s="7" t="n">
+        <v>0.03000000706058618</v>
+      </c>
+      <c r="G115" s="4" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="H115" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I115" s="2" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" s="2" t="inlineStr">
@@ -6585,24 +4805,20 @@
         <v>14163130</v>
       </c>
       <c r="E116" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="F116" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G116" s="6" t="n">
         <v>13738236</v>
       </c>
-      <c r="H116" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I116" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F116" s="7" t="n">
+        <v>0.03000000706058618</v>
+      </c>
+      <c r="G116" s="4" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="H116" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I116" s="2" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="2" t="inlineStr">
@@ -6624,24 +4840,20 @@
         <v>14163130</v>
       </c>
       <c r="E117" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="F117" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G117" s="6" t="n">
         <v>13738236</v>
       </c>
-      <c r="H117" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I117" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F117" s="7" t="n">
+        <v>0.03000000706058618</v>
+      </c>
+      <c r="G117" s="4" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="H117" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I117" s="2" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="2" t="inlineStr">
@@ -6663,24 +4875,20 @@
         <v>14163130</v>
       </c>
       <c r="E118" s="4" t="n">
-        <v>13879867.4</v>
-      </c>
-      <c r="F118" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G118" s="6" t="n">
         <v>13738236</v>
       </c>
-      <c r="H118" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I118" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F118" s="7" t="n">
+        <v>0.03000000706058618</v>
+      </c>
+      <c r="G118" s="4" t="n">
+        <v>13738236</v>
+      </c>
+      <c r="H118" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I118" s="2" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="2" t="inlineStr">
@@ -6704,7 +4912,7 @@
       <c r="E119" s="4" t="n">
         <v>22607755.701</v>
       </c>
-      <c r="F119" s="5" t="n">
+      <c r="F119" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G119" s="4" t="n">
@@ -6739,7 +4947,7 @@
       <c r="E120" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F120" s="5" t="n">
+      <c r="F120" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G120" s="4" t="n">
@@ -6774,7 +4982,7 @@
       <c r="E121" s="4" t="n">
         <v>2825961.998</v>
       </c>
-      <c r="F121" s="5" t="n">
+      <c r="F121" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G121" s="4" t="n">
@@ -6807,24 +5015,20 @@
         <v>5343190</v>
       </c>
       <c r="E122" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="F122" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G122" s="6" t="n">
         <v>5182894</v>
       </c>
-      <c r="H122" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I122" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F122" s="7" t="n">
+        <v>0.03000005614623474</v>
+      </c>
+      <c r="G122" s="4" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="H122" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I122" s="2" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="2" t="inlineStr">
@@ -6846,24 +5050,20 @@
         <v>5343190</v>
       </c>
       <c r="E123" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="F123" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G123" s="6" t="n">
         <v>5182894</v>
       </c>
-      <c r="H123" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I123" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F123" s="7" t="n">
+        <v>0.03000005614623474</v>
+      </c>
+      <c r="G123" s="4" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="H123" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I123" s="2" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="2" t="inlineStr">
@@ -6885,24 +5085,20 @@
         <v>5343190</v>
       </c>
       <c r="E124" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="F124" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G124" s="6" t="n">
         <v>5182894</v>
       </c>
-      <c r="H124" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I124" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F124" s="7" t="n">
+        <v>0.03000005614623474</v>
+      </c>
+      <c r="G124" s="4" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="H124" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I124" s="2" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="2" t="inlineStr">
@@ -6926,7 +5122,7 @@
       <c r="E125" s="4" t="n">
         <v>467968.005</v>
       </c>
-      <c r="F125" s="5" t="n">
+      <c r="F125" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G125" s="4" t="n">
@@ -6961,7 +5157,7 @@
       <c r="E126" s="4" t="n">
         <v>467968.005</v>
       </c>
-      <c r="F126" s="5" t="n">
+      <c r="F126" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G126" s="4" t="n">
@@ -6996,7 +5192,7 @@
       <c r="E127" s="4" t="n">
         <v>467968.005</v>
       </c>
-      <c r="F127" s="5" t="n">
+      <c r="F127" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G127" s="4" t="n">
@@ -7031,7 +5227,7 @@
       <c r="E128" s="4" t="n">
         <v>274752</v>
       </c>
-      <c r="F128" s="5" t="n">
+      <c r="F128" s="7" t="n">
         <v>0.232</v>
       </c>
       <c r="G128" s="4" t="n">
@@ -7066,7 +5262,7 @@
       <c r="E129" s="4" t="n">
         <v>274752</v>
       </c>
-      <c r="F129" s="5" t="n">
+      <c r="F129" s="7" t="n">
         <v>0.232</v>
       </c>
       <c r="G129" s="4" t="n">
@@ -7101,7 +5297,7 @@
       <c r="E130" s="4" t="n">
         <v>274752</v>
       </c>
-      <c r="F130" s="5" t="n">
+      <c r="F130" s="7" t="n">
         <v>0.232</v>
       </c>
       <c r="G130" s="4" t="n">
@@ -7136,7 +5332,7 @@
       <c r="E131" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F131" s="5" t="n">
+      <c r="F131" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G131" s="4" t="n">
@@ -7171,7 +5367,7 @@
       <c r="E132" s="4" t="n">
         <v>189891.529</v>
       </c>
-      <c r="F132" s="5" t="n">
+      <c r="F132" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G132" s="4" t="n">
@@ -7206,7 +5402,7 @@
       <c r="E133" s="4" t="n">
         <v>189891.529</v>
       </c>
-      <c r="F133" s="5" t="n">
+      <c r="F133" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G133" s="4" t="n">
@@ -7241,7 +5437,7 @@
       <c r="E134" s="4" t="n">
         <v>189891.529</v>
       </c>
-      <c r="F134" s="5" t="n">
+      <c r="F134" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G134" s="4" t="n">
@@ -7276,7 +5472,7 @@
       <c r="E135" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F135" s="5" t="n">
+      <c r="F135" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G135" s="4" t="n">
@@ -7311,7 +5507,7 @@
       <c r="E136" s="4" t="n">
         <v>189891.529</v>
       </c>
-      <c r="F136" s="5" t="n">
+      <c r="F136" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G136" s="4" t="n">
@@ -7346,7 +5542,7 @@
       <c r="E137" s="4" t="n">
         <v>189891.529</v>
       </c>
-      <c r="F137" s="5" t="n">
+      <c r="F137" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G137" s="4" t="n">
@@ -7381,7 +5577,7 @@
       <c r="E138" s="4" t="n">
         <v>1661659.649</v>
       </c>
-      <c r="F138" s="5" t="n">
+      <c r="F138" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G138" s="4" t="n">
@@ -7416,7 +5612,7 @@
       <c r="E139" s="4" t="n">
         <v>189891.529</v>
       </c>
-      <c r="F139" s="5" t="n">
+      <c r="F139" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G139" s="4" t="n">
@@ -7451,7 +5647,7 @@
       <c r="E140" s="4" t="n">
         <v>196665.143</v>
       </c>
-      <c r="F140" s="5" t="n">
+      <c r="F140" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G140" s="4" t="n">
@@ -7486,7 +5682,7 @@
       <c r="E141" s="4" t="n">
         <v>196665.143</v>
       </c>
-      <c r="F141" s="5" t="n">
+      <c r="F141" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G141" s="4" t="n">
@@ -7521,7 +5717,7 @@
       <c r="E142" s="4" t="n">
         <v>196665.143</v>
       </c>
-      <c r="F142" s="5" t="n">
+      <c r="F142" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G142" s="4" t="n">
@@ -7556,7 +5752,7 @@
       <c r="E143" s="4" t="n">
         <v>196665.143</v>
       </c>
-      <c r="F143" s="5" t="n">
+      <c r="F143" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G143" s="4" t="n">
@@ -7591,7 +5787,7 @@
       <c r="E144" s="4" t="n">
         <v>467968.005</v>
       </c>
-      <c r="F144" s="5" t="n">
+      <c r="F144" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G144" s="4" t="n">
@@ -7624,15 +5820,15 @@
         <v>548550</v>
       </c>
       <c r="E145" s="4" t="n">
-        <v>634418</v>
-      </c>
-      <c r="F145" s="5" t="n">
-        <v>-0.1565363230334518</v>
-      </c>
-      <c r="G145" s="9" t="n">
+        <v>467968</v>
+      </c>
+      <c r="F145" s="7" t="n">
+        <v>0.1469000091149394</v>
+      </c>
+      <c r="G145" s="6" t="n">
         <v>467968.005</v>
       </c>
-      <c r="H145" s="3" t="inlineStr">
+      <c r="H145" s="8" t="inlineStr">
         <is>
           <t>표기오류 수정 제시</t>
         </is>
@@ -7665,7 +5861,7 @@
       <c r="E146" s="4" t="n">
         <v>460782</v>
       </c>
-      <c r="F146" s="5" t="n">
+      <c r="F146" s="7" t="n">
         <v>0.16</v>
       </c>
       <c r="G146" s="4" t="n">
@@ -7698,15 +5894,15 @@
         <v>123210</v>
       </c>
       <c r="E147" s="4" t="n">
-        <v>634418</v>
-      </c>
-      <c r="F147" s="5" t="n">
-        <v>-4.149078808538268</v>
-      </c>
-      <c r="G147" s="9" t="n">
+        <v>105110</v>
+      </c>
+      <c r="F147" s="7" t="n">
+        <v>0.1469036604171739</v>
+      </c>
+      <c r="G147" s="6" t="n">
         <v>105110.451</v>
       </c>
-      <c r="H147" s="3" t="inlineStr">
+      <c r="H147" s="8" t="inlineStr">
         <is>
           <t>표기오류 수정 제시</t>
         </is>
@@ -7739,7 +5935,7 @@
       <c r="E148" s="4" t="n">
         <v>105110.451</v>
       </c>
-      <c r="F148" s="5" t="n">
+      <c r="F148" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G148" s="4" t="n">
@@ -7774,7 +5970,7 @@
       <c r="E149" s="4" t="n">
         <v>105110.451</v>
       </c>
-      <c r="F149" s="5" t="n">
+      <c r="F149" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G149" s="4" t="n">
@@ -7809,7 +6005,7 @@
       <c r="E150" s="4" t="n">
         <v>46784.004</v>
       </c>
-      <c r="F150" s="5" t="n">
+      <c r="F150" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G150" s="4" t="n">
@@ -7844,7 +6040,7 @@
       <c r="E151" s="4" t="n">
         <v>46784.004</v>
       </c>
-      <c r="F151" s="5" t="n">
+      <c r="F151" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G151" s="4" t="n">
@@ -7879,7 +6075,7 @@
       <c r="E152" s="4" t="n">
         <v>46784.004</v>
       </c>
-      <c r="F152" s="5" t="n">
+      <c r="F152" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G152" s="4" t="n">
@@ -7914,7 +6110,7 @@
       <c r="E153" s="4" t="n">
         <v>101732.175</v>
       </c>
-      <c r="F153" s="5" t="n">
+      <c r="F153" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G153" s="4" t="n">
@@ -7949,7 +6145,7 @@
       <c r="E154" s="4" t="n">
         <v>644312.306</v>
       </c>
-      <c r="F154" s="5" t="n">
+      <c r="F154" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G154" s="4" t="n">
@@ -7984,7 +6180,7 @@
       <c r="E155" s="4" t="n">
         <v>644312.306</v>
       </c>
-      <c r="F155" s="5" t="n">
+      <c r="F155" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G155" s="4" t="n">
@@ -8019,7 +6215,7 @@
       <c r="E156" s="4" t="n">
         <v>644312.306</v>
       </c>
-      <c r="F156" s="5" t="n">
+      <c r="F156" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G156" s="4" t="n">
@@ -8054,7 +6250,7 @@
       <c r="E157" s="4" t="n">
         <v>685286.699</v>
       </c>
-      <c r="F157" s="5" t="n">
+      <c r="F157" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G157" s="4" t="n">
@@ -8089,7 +6285,7 @@
       <c r="E158" s="4" t="n">
         <v>685286.699</v>
       </c>
-      <c r="F158" s="5" t="n">
+      <c r="F158" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G158" s="4" t="n">
@@ -8124,7 +6320,7 @@
       <c r="E159" s="4" t="n">
         <v>685286.699</v>
       </c>
-      <c r="F159" s="5" t="n">
+      <c r="F159" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G159" s="4" t="n">
@@ -8159,7 +6355,7 @@
       <c r="E160" s="4" t="n">
         <v>685286.699</v>
       </c>
-      <c r="F160" s="5" t="n">
+      <c r="F160" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G160" s="4" t="n">
@@ -8194,7 +6390,7 @@
       <c r="E161" s="4" t="n">
         <v>1328199.921</v>
       </c>
-      <c r="F161" s="5" t="n">
+      <c r="F161" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G161" s="4" t="n">
@@ -8229,7 +6425,7 @@
       <c r="E162" s="4" t="n">
         <v>1328199.921</v>
       </c>
-      <c r="F162" s="5" t="n">
+      <c r="F162" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G162" s="4" t="n">
@@ -8264,7 +6460,7 @@
       <c r="E163" s="4" t="n">
         <v>1328199.921</v>
       </c>
-      <c r="F163" s="5" t="n">
+      <c r="F163" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G163" s="4" t="n">
@@ -8299,7 +6495,7 @@
       <c r="E164" s="4" t="n">
         <v>1328199.921</v>
       </c>
-      <c r="F164" s="5" t="n">
+      <c r="F164" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G164" s="4" t="n">
@@ -8334,7 +6530,7 @@
       <c r="E165" s="4" t="n">
         <v>2580098.578</v>
       </c>
-      <c r="F165" s="5" t="n">
+      <c r="F165" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G165" s="4" t="n">
@@ -8367,24 +6563,20 @@
         <v>3024380</v>
       </c>
       <c r="E166" s="4" t="n">
-        <v>2963892.4</v>
-      </c>
-      <c r="F166" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G166" s="6" t="n">
         <v>2933649</v>
       </c>
-      <c r="H166" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I166" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F166" s="7" t="n">
+        <v>0.02999986774148751</v>
+      </c>
+      <c r="G166" s="4" t="n">
+        <v>2933649</v>
+      </c>
+      <c r="H166" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I166" s="2" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" s="2" t="inlineStr">
@@ -8406,24 +6598,20 @@
         <v>3024380</v>
       </c>
       <c r="E167" s="4" t="n">
-        <v>2963892.4</v>
-      </c>
-      <c r="F167" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G167" s="6" t="n">
         <v>2933649</v>
       </c>
-      <c r="H167" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I167" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F167" s="7" t="n">
+        <v>0.02999986774148751</v>
+      </c>
+      <c r="G167" s="4" t="n">
+        <v>2933649</v>
+      </c>
+      <c r="H167" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I167" s="2" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="2" t="inlineStr">
@@ -8445,24 +6633,20 @@
         <v>3024380</v>
       </c>
       <c r="E168" s="4" t="n">
-        <v>2963892.4</v>
-      </c>
-      <c r="F168" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G168" s="6" t="n">
         <v>2933649</v>
       </c>
-      <c r="H168" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I168" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F168" s="7" t="n">
+        <v>0.02999986774148751</v>
+      </c>
+      <c r="G168" s="4" t="n">
+        <v>2933649</v>
+      </c>
+      <c r="H168" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I168" s="2" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="2" t="inlineStr">
@@ -8484,24 +6668,20 @@
         <v>5343190</v>
       </c>
       <c r="E169" s="4" t="n">
-        <v>5236326.2</v>
-      </c>
-      <c r="F169" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G169" s="6" t="n">
         <v>5182894</v>
       </c>
-      <c r="H169" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I169" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F169" s="7" t="n">
+        <v>0.03000005614623474</v>
+      </c>
+      <c r="G169" s="4" t="n">
+        <v>5182894</v>
+      </c>
+      <c r="H169" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I169" s="2" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="2" t="inlineStr">
@@ -8525,7 +6705,7 @@
       <c r="E170" s="4" t="n">
         <v>6986.889</v>
       </c>
-      <c r="F170" s="5" t="n">
+      <c r="F170" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G170" s="4" t="n">
@@ -8560,7 +6740,7 @@
       <c r="E171" s="4" t="n">
         <v>27111.518</v>
       </c>
-      <c r="F171" s="5" t="n">
+      <c r="F171" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G171" s="4" t="n">
@@ -8595,7 +6775,7 @@
       <c r="E172" s="4" t="n">
         <v>11018921.123</v>
       </c>
-      <c r="F172" s="5" t="n">
+      <c r="F172" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G172" s="4" t="n">
@@ -8630,7 +6810,7 @@
       <c r="E173" s="4" t="n">
         <v>11018921.123</v>
       </c>
-      <c r="F173" s="5" t="n">
+      <c r="F173" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G173" s="4" t="n">
@@ -8665,7 +6845,7 @@
       <c r="E174" s="4" t="n">
         <v>11018921.123</v>
       </c>
-      <c r="F174" s="5" t="n">
+      <c r="F174" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G174" s="4" t="n">
@@ -8700,7 +6880,7 @@
       <c r="E175" s="4" t="n">
         <v>11018921.123</v>
       </c>
-      <c r="F175" s="5" t="n">
+      <c r="F175" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G175" s="4" t="n">
@@ -8735,7 +6915,7 @@
       <c r="E176" s="4" t="n">
         <v>11018921.123</v>
       </c>
-      <c r="F176" s="5" t="n">
+      <c r="F176" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G176" s="4" t="n">
@@ -8770,7 +6950,7 @@
       <c r="E177" s="4" t="n">
         <v>11018921.123</v>
       </c>
-      <c r="F177" s="5" t="n">
+      <c r="F177" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G177" s="4" t="n">
@@ -8805,7 +6985,7 @@
       <c r="E178" s="4" t="n">
         <v>11018921.123</v>
       </c>
-      <c r="F178" s="5" t="n">
+      <c r="F178" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G178" s="4" t="n">
@@ -8840,7 +7020,7 @@
       <c r="E179" s="4" t="n">
         <v>11018921.123</v>
       </c>
-      <c r="F179" s="5" t="n">
+      <c r="F179" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G179" s="4" t="n">
@@ -8875,7 +7055,7 @@
       <c r="E180" s="4" t="n">
         <v>100409.87</v>
       </c>
-      <c r="F180" s="5" t="n">
+      <c r="F180" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G180" s="4" t="n">
@@ -8910,7 +7090,7 @@
       <c r="E181" s="4" t="n">
         <v>794961.235</v>
       </c>
-      <c r="F181" s="5" t="n">
+      <c r="F181" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G181" s="4" t="n">
@@ -8945,7 +7125,7 @@
       <c r="E182" s="4" t="n">
         <v>985543.775</v>
       </c>
-      <c r="F182" s="5" t="n">
+      <c r="F182" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G182" s="4" t="n">
@@ -8980,7 +7160,7 @@
       <c r="E183" s="4" t="n">
         <v>794961.235</v>
       </c>
-      <c r="F183" s="5" t="n">
+      <c r="F183" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G183" s="4" t="n">
@@ -9015,7 +7195,7 @@
       <c r="E184" s="4" t="n">
         <v>985543.775</v>
       </c>
-      <c r="F184" s="5" t="n">
+      <c r="F184" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G184" s="4" t="n">
@@ -9050,7 +7230,7 @@
       <c r="E185" s="4" t="n">
         <v>97910.287</v>
       </c>
-      <c r="F185" s="5" t="n">
+      <c r="F185" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G185" s="4" t="n">
@@ -9085,7 +7265,7 @@
       <c r="E186" s="4" t="n">
         <v>97927.349</v>
       </c>
-      <c r="F186" s="5" t="n">
+      <c r="F186" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G186" s="4" t="n">
@@ -9120,7 +7300,7 @@
       <c r="E187" s="4" t="n">
         <v>53344.343</v>
       </c>
-      <c r="F187" s="5" t="n">
+      <c r="F187" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G187" s="4" t="n">
@@ -9155,7 +7335,7 @@
       <c r="E188" s="4" t="n">
         <v>378332.788</v>
       </c>
-      <c r="F188" s="5" t="n">
+      <c r="F188" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G188" s="4" t="n">
@@ -9190,7 +7370,7 @@
       <c r="E189" s="4" t="n">
         <v>104257.351</v>
       </c>
-      <c r="F189" s="5" t="n">
+      <c r="F189" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G189" s="4" t="n">
@@ -9225,7 +7405,7 @@
       <c r="E190" s="4" t="n">
         <v>113172.246</v>
       </c>
-      <c r="F190" s="5" t="n">
+      <c r="F190" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G190" s="4" t="n">
@@ -9260,7 +7440,7 @@
       <c r="E191" s="4" t="n">
         <v>206637.882</v>
       </c>
-      <c r="F191" s="5" t="n">
+      <c r="F191" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G191" s="4" t="n">
@@ -9295,7 +7475,7 @@
       <c r="E192" s="4" t="n">
         <v>24142.73</v>
       </c>
-      <c r="F192" s="5" t="n">
+      <c r="F192" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G192" s="4" t="n">
@@ -9330,7 +7510,7 @@
       <c r="E193" s="4" t="n">
         <v>10151.89</v>
       </c>
-      <c r="F193" s="5" t="n">
+      <c r="F193" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G193" s="4" t="n">
@@ -9365,7 +7545,7 @@
       <c r="E194" s="4" t="n">
         <v>3165.001</v>
       </c>
-      <c r="F194" s="5" t="n">
+      <c r="F194" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G194" s="4" t="n">
@@ -9400,7 +7580,7 @@
       <c r="E195" s="4" t="n">
         <v>49530.986</v>
       </c>
-      <c r="F195" s="5" t="n">
+      <c r="F195" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G195" s="4" t="n">
@@ -9435,7 +7615,7 @@
       <c r="E196" s="4" t="n">
         <v>43900.526</v>
       </c>
-      <c r="F196" s="5" t="n">
+      <c r="F196" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G196" s="4" t="n">
@@ -9470,7 +7650,7 @@
       <c r="E197" s="4" t="n">
         <v>610393.05</v>
       </c>
-      <c r="F197" s="5" t="n">
+      <c r="F197" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G197" s="4" t="n">
@@ -9505,7 +7685,7 @@
       <c r="E198" s="4" t="n">
         <v>432368.142</v>
       </c>
-      <c r="F198" s="5" t="n">
+      <c r="F198" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G198" s="4" t="n">
@@ -9540,7 +7720,7 @@
       <c r="E199" s="4" t="n">
         <v>219349.072</v>
       </c>
-      <c r="F199" s="5" t="n">
+      <c r="F199" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G199" s="4" t="n">
@@ -9575,7 +7755,7 @@
       <c r="E200" s="4" t="n">
         <v>154496.41</v>
       </c>
-      <c r="F200" s="5" t="n">
+      <c r="F200" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G200" s="4" t="n">
@@ -9610,7 +7790,7 @@
       <c r="E201" s="4" t="n">
         <v>141785.22</v>
       </c>
-      <c r="F201" s="5" t="n">
+      <c r="F201" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G201" s="4" t="n">
@@ -9645,7 +7825,7 @@
       <c r="E202" s="4" t="n">
         <v>141785.22</v>
       </c>
-      <c r="F202" s="5" t="n">
+      <c r="F202" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G202" s="4" t="n">
@@ -9680,7 +7860,7 @@
       <c r="E203" s="4" t="n">
         <v>125883.436</v>
       </c>
-      <c r="F203" s="5" t="n">
+      <c r="F203" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G203" s="4" t="n">
@@ -9715,7 +7895,7 @@
       <c r="E204" s="4" t="n">
         <v>183749.209</v>
       </c>
-      <c r="F204" s="5" t="n">
+      <c r="F204" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G204" s="4" t="n">
@@ -9750,7 +7930,7 @@
       <c r="E205" s="4" t="n">
         <v>459735.59</v>
       </c>
-      <c r="F205" s="5" t="n">
+      <c r="F205" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G205" s="4" t="n">
@@ -9785,7 +7965,7 @@
       <c r="E206" s="4" t="n">
         <v>546069.3100000001</v>
       </c>
-      <c r="F206" s="5" t="n">
+      <c r="F206" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G206" s="4" t="n">
@@ -9820,7 +8000,7 @@
       <c r="E207" s="4" t="n">
         <v>602570.123</v>
       </c>
-      <c r="F207" s="5" t="n">
+      <c r="F207" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G207" s="4" t="n">
@@ -9855,7 +8035,7 @@
       <c r="E208" s="4" t="n">
         <v>2485694.532</v>
       </c>
-      <c r="F208" s="5" t="n">
+      <c r="F208" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G208" s="4" t="n">
@@ -9890,7 +8070,7 @@
       <c r="E209" s="4" t="n">
         <v>155631.033</v>
       </c>
-      <c r="F209" s="5" t="n">
+      <c r="F209" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G209" s="4" t="n">
@@ -9925,7 +8105,7 @@
       <c r="E210" s="4" t="n">
         <v>161909.849</v>
       </c>
-      <c r="F210" s="5" t="n">
+      <c r="F210" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G210" s="4" t="n">
@@ -9960,7 +8140,7 @@
       <c r="E211" s="4" t="n">
         <v>4384.934</v>
       </c>
-      <c r="F211" s="5" t="n">
+      <c r="F211" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G211" s="4" t="n">
@@ -9995,7 +8175,7 @@
       <c r="E212" s="4" t="n">
         <v>7515.811</v>
       </c>
-      <c r="F212" s="5" t="n">
+      <c r="F212" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G212" s="4" t="n">
@@ -10030,7 +8210,7 @@
       <c r="E213" s="4" t="n">
         <v>15679.978</v>
       </c>
-      <c r="F213" s="5" t="n">
+      <c r="F213" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G213" s="4" t="n">
@@ -10065,7 +8245,7 @@
       <c r="E214" s="4" t="n">
         <v>53335.812</v>
       </c>
-      <c r="F214" s="5" t="n">
+      <c r="F214" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G214" s="4" t="n">
@@ -10100,7 +8280,7 @@
       <c r="E215" s="4" t="n">
         <v>207090.025</v>
       </c>
-      <c r="F215" s="5" t="n">
+      <c r="F215" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G215" s="4" t="n">
@@ -10135,7 +8315,7 @@
       <c r="E216" s="4" t="n">
         <v>445011.084</v>
       </c>
-      <c r="F216" s="5" t="n">
+      <c r="F216" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G216" s="4" t="n">
@@ -10170,7 +8350,7 @@
       <c r="E217" s="4" t="n">
         <v>683179.542</v>
       </c>
-      <c r="F217" s="5" t="n">
+      <c r="F217" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G217" s="4" t="n">
@@ -10205,7 +8385,7 @@
       <c r="E218" s="4" t="n">
         <v>2572207.403</v>
       </c>
-      <c r="F218" s="5" t="n">
+      <c r="F218" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G218" s="4" t="n">
@@ -10240,7 +8420,7 @@
       <c r="E219" s="4" t="n">
         <v>3333616.215</v>
       </c>
-      <c r="F219" s="5" t="n">
+      <c r="F219" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G219" s="4" t="n">
@@ -10275,7 +8455,7 @@
       <c r="E220" s="4" t="n">
         <v>3333616.215</v>
       </c>
-      <c r="F220" s="5" t="n">
+      <c r="F220" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G220" s="4" t="n">
@@ -10310,7 +8490,7 @@
       <c r="E221" s="4" t="n">
         <v>4001875.038</v>
       </c>
-      <c r="F221" s="5" t="n">
+      <c r="F221" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G221" s="4" t="n">
@@ -10345,7 +8525,7 @@
       <c r="E222" s="4" t="n">
         <v>819376.9569999999</v>
       </c>
-      <c r="F222" s="5" t="n">
+      <c r="F222" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G222" s="4" t="n">
@@ -10380,7 +8560,7 @@
       <c r="E223" s="4" t="n">
         <v>1376562.16</v>
       </c>
-      <c r="F223" s="5" t="n">
+      <c r="F223" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G223" s="4" t="n">
@@ -10415,7 +8595,7 @@
       <c r="E224" s="4" t="n">
         <v>1062425.147</v>
       </c>
-      <c r="F224" s="5" t="n">
+      <c r="F224" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G224" s="4" t="n">
@@ -10450,7 +8630,7 @@
       <c r="E225" s="4" t="n">
         <v>581208.499</v>
       </c>
-      <c r="F225" s="5" t="n">
+      <c r="F225" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G225" s="4" t="n">
@@ -10485,7 +8665,7 @@
       <c r="E226" s="4" t="n">
         <v>581208.499</v>
       </c>
-      <c r="F226" s="5" t="n">
+      <c r="F226" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G226" s="4" t="n">
@@ -10520,7 +8700,7 @@
       <c r="E227" s="4" t="n">
         <v>251997.209</v>
       </c>
-      <c r="F227" s="5" t="n">
+      <c r="F227" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G227" s="4" t="n">
@@ -10555,7 +8735,7 @@
       <c r="E228" s="4" t="n">
         <v>196648.081</v>
       </c>
-      <c r="F228" s="5" t="n">
+      <c r="F228" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G228" s="4" t="n">
@@ -10590,7 +8770,7 @@
       <c r="E229" s="4" t="n">
         <v>64818.538</v>
       </c>
-      <c r="F229" s="5" t="n">
+      <c r="F229" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G229" s="4" t="n">
@@ -10625,7 +8805,7 @@
       <c r="E230" s="4" t="n">
         <v>56807.929</v>
       </c>
-      <c r="F230" s="5" t="n">
+      <c r="F230" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G230" s="4" t="n">
@@ -10660,7 +8840,7 @@
       <c r="E231" s="4" t="n">
         <v>70645.211</v>
       </c>
-      <c r="F231" s="5" t="n">
+      <c r="F231" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G231" s="4" t="n">
@@ -10695,7 +8875,7 @@
       <c r="E232" s="4" t="n">
         <v>21847.891</v>
       </c>
-      <c r="F232" s="5" t="n">
+      <c r="F232" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G232" s="4" t="n">
@@ -10730,7 +8910,7 @@
       <c r="E233" s="4" t="n">
         <v>36410.308</v>
       </c>
-      <c r="F233" s="5" t="n">
+      <c r="F233" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G233" s="4" t="n">
@@ -10765,7 +8945,7 @@
       <c r="E234" s="4" t="n">
         <v>49155.622</v>
       </c>
-      <c r="F234" s="5" t="n">
+      <c r="F234" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G234" s="4" t="n">
@@ -10800,7 +8980,7 @@
       <c r="E235" s="4" t="n">
         <v>4191749.505</v>
       </c>
-      <c r="F235" s="5" t="n">
+      <c r="F235" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G235" s="4" t="n">
@@ -10835,7 +9015,7 @@
       <c r="E236" s="4" t="n">
         <v>19663.955</v>
       </c>
-      <c r="F236" s="5" t="n">
+      <c r="F236" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G236" s="4" t="n">
@@ -10870,7 +9050,7 @@
       <c r="E237" s="4" t="n">
         <v>1883849.544</v>
       </c>
-      <c r="F237" s="5" t="n">
+      <c r="F237" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G237" s="4" t="n">
@@ -10905,7 +9085,7 @@
       <c r="E238" s="4" t="n">
         <v>2150938.092</v>
       </c>
-      <c r="F238" s="5" t="n">
+      <c r="F238" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G238" s="4" t="n">
@@ -10940,7 +9120,7 @@
       <c r="E239" s="4" t="n">
         <v>3100404.268</v>
       </c>
-      <c r="F239" s="5" t="n">
+      <c r="F239" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G239" s="4" t="n">
@@ -10975,7 +9155,7 @@
       <c r="E240" s="4" t="n">
         <v>3180305.614</v>
       </c>
-      <c r="F240" s="5" t="n">
+      <c r="F240" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G240" s="4" t="n">
@@ -11010,7 +9190,7 @@
       <c r="E241" s="4" t="n">
         <v>3232233.811</v>
       </c>
-      <c r="F241" s="5" t="n">
+      <c r="F241" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G241" s="4" t="n">
@@ -11045,7 +9225,7 @@
       <c r="E242" s="4" t="n">
         <v>1162937.389</v>
       </c>
-      <c r="F242" s="5" t="n">
+      <c r="F242" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G242" s="4" t="n">
@@ -11080,7 +9260,7 @@
       <c r="E243" s="4" t="n">
         <v>1162937.389</v>
       </c>
-      <c r="F243" s="5" t="n">
+      <c r="F243" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G243" s="4" t="n">
@@ -11115,7 +9295,7 @@
       <c r="E244" s="4" t="n">
         <v>1200670.002</v>
       </c>
-      <c r="F244" s="5" t="n">
+      <c r="F244" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G244" s="4" t="n">
@@ -11150,7 +9330,7 @@
       <c r="E245" s="4" t="n">
         <v>1200670.002</v>
       </c>
-      <c r="F245" s="5" t="n">
+      <c r="F245" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G245" s="4" t="n">
@@ -11185,7 +9365,7 @@
       <c r="E246" s="4" t="n">
         <v>1200670.002</v>
       </c>
-      <c r="F246" s="5" t="n">
+      <c r="F246" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G246" s="4" t="n">
@@ -11220,7 +9400,7 @@
       <c r="E247" s="4" t="n">
         <v>1200670.002</v>
       </c>
-      <c r="F247" s="5" t="n">
+      <c r="F247" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G247" s="4" t="n">
@@ -11255,7 +9435,7 @@
       <c r="E248" s="4" t="n">
         <v>1174667.514</v>
       </c>
-      <c r="F248" s="5" t="n">
+      <c r="F248" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G248" s="4" t="n">
@@ -11290,7 +9470,7 @@
       <c r="E249" s="4" t="n">
         <v>1174667.514</v>
       </c>
-      <c r="F249" s="5" t="n">
+      <c r="F249" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G249" s="4" t="n">
@@ -11325,7 +9505,7 @@
       <c r="E250" s="4" t="n">
         <v>1174667.514</v>
       </c>
-      <c r="F250" s="5" t="n">
+      <c r="F250" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G250" s="4" t="n">
@@ -11360,7 +9540,7 @@
       <c r="E251" s="4" t="n">
         <v>1174667.514</v>
       </c>
-      <c r="F251" s="5" t="n">
+      <c r="F251" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G251" s="4" t="n">
@@ -11395,7 +9575,7 @@
       <c r="E252" s="4" t="n">
         <v>1305328.31</v>
       </c>
-      <c r="F252" s="5" t="n">
+      <c r="F252" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G252" s="4" t="n">
@@ -11430,7 +9610,7 @@
       <c r="E253" s="4" t="n">
         <v>1305328.31</v>
       </c>
-      <c r="F253" s="5" t="n">
+      <c r="F253" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G253" s="4" t="n">
@@ -11465,7 +9645,7 @@
       <c r="E254" s="4" t="n">
         <v>1382900.693</v>
       </c>
-      <c r="F254" s="5" t="n">
+      <c r="F254" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G254" s="4" t="n">
@@ -11500,7 +9680,7 @@
       <c r="E255" s="4" t="n">
         <v>1382900.693</v>
       </c>
-      <c r="F255" s="5" t="n">
+      <c r="F255" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G255" s="4" t="n">
@@ -11535,7 +9715,7 @@
       <c r="E256" s="4" t="n">
         <v>339533.8</v>
       </c>
-      <c r="F256" s="5" t="n">
+      <c r="F256" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G256" s="4" t="n">
@@ -11570,7 +9750,7 @@
       <c r="E257" s="4" t="n">
         <v>339533.8</v>
       </c>
-      <c r="F257" s="5" t="n">
+      <c r="F257" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G257" s="4" t="n">
@@ -11605,7 +9785,7 @@
       <c r="E258" s="4" t="n">
         <v>390532.118</v>
       </c>
-      <c r="F258" s="5" t="n">
+      <c r="F258" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G258" s="4" t="n">
@@ -11640,7 +9820,7 @@
       <c r="E259" s="4" t="n">
         <v>418496.736</v>
       </c>
-      <c r="F259" s="5" t="n">
+      <c r="F259" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G259" s="4" t="n">
@@ -11675,7 +9855,7 @@
       <c r="E260" s="4" t="n">
         <v>5894.921</v>
       </c>
-      <c r="F260" s="5" t="n">
+      <c r="F260" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G260" s="4" t="n">
@@ -11710,7 +9890,7 @@
       <c r="E261" s="4" t="n">
         <v>19663.955</v>
       </c>
-      <c r="F261" s="5" t="n">
+      <c r="F261" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G261" s="4" t="n">
@@ -11745,7 +9925,7 @@
       <c r="E262" s="4" t="n">
         <v>49155.622</v>
       </c>
-      <c r="F262" s="5" t="n">
+      <c r="F262" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G262" s="4" t="n">
@@ -11780,7 +9960,7 @@
       <c r="E263" s="4" t="n">
         <v>290309.93</v>
       </c>
-      <c r="F263" s="5" t="n">
+      <c r="F263" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G263" s="4" t="n">
@@ -11815,7 +9995,7 @@
       <c r="E264" s="4" t="n">
         <v>361543.78</v>
       </c>
-      <c r="F264" s="5" t="n">
+      <c r="F264" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G264" s="4" t="n">
@@ -11850,7 +10030,7 @@
       <c r="E265" s="4" t="n">
         <v>387691.295</v>
       </c>
-      <c r="F265" s="5" t="n">
+      <c r="F265" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G265" s="4" t="n">
@@ -11885,7 +10065,7 @@
       <c r="E266" s="4" t="n">
         <v>36265.281</v>
       </c>
-      <c r="F266" s="5" t="n">
+      <c r="F266" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G266" s="4" t="n">
@@ -11920,7 +10100,7 @@
       <c r="E267" s="4" t="n">
         <v>33646.264</v>
       </c>
-      <c r="F267" s="5" t="n">
+      <c r="F267" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G267" s="4" t="n">
@@ -11955,7 +10135,7 @@
       <c r="E268" s="4" t="n">
         <v>32477.517</v>
       </c>
-      <c r="F268" s="5" t="n">
+      <c r="F268" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G268" s="4" t="n">
@@ -11990,7 +10170,7 @@
       <c r="E269" s="4" t="n">
         <v>300794.529</v>
       </c>
-      <c r="F269" s="5" t="n">
+      <c r="F269" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G269" s="4" t="n">
@@ -12025,7 +10205,7 @@
       <c r="E270" s="4" t="n">
         <v>289874.849</v>
       </c>
-      <c r="F270" s="5" t="n">
+      <c r="F270" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G270" s="4" t="n">
@@ -12060,7 +10240,7 @@
       <c r="E271" s="4" t="n">
         <v>286957.247</v>
       </c>
-      <c r="F271" s="5" t="n">
+      <c r="F271" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G271" s="4" t="n">
@@ -12095,7 +10275,7 @@
       <c r="E272" s="4" t="n">
         <v>39327.91</v>
       </c>
-      <c r="F272" s="5" t="n">
+      <c r="F272" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G272" s="4" t="n">
@@ -12130,7 +10310,7 @@
       <c r="E273" s="4" t="n">
         <v>38594.244</v>
       </c>
-      <c r="F273" s="5" t="n">
+      <c r="F273" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G273" s="4" t="n">
@@ -12165,7 +10345,7 @@
       <c r="E274" s="4" t="n">
         <v>37869.109</v>
       </c>
-      <c r="F274" s="5" t="n">
+      <c r="F274" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G274" s="4" t="n">
@@ -12200,7 +10380,7 @@
       <c r="E275" s="4" t="n">
         <v>58258.199</v>
       </c>
-      <c r="F275" s="5" t="n">
+      <c r="F275" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G275" s="4" t="n">
@@ -12235,7 +10415,7 @@
       <c r="E276" s="4" t="n">
         <v>58258.199</v>
       </c>
-      <c r="F276" s="5" t="n">
+      <c r="F276" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G276" s="4" t="n">
@@ -12270,7 +10450,7 @@
       <c r="E277" s="4" t="n">
         <v>58258.199</v>
       </c>
-      <c r="F277" s="5" t="n">
+      <c r="F277" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G277" s="4" t="n">
@@ -12305,7 +10485,7 @@
       <c r="E278" s="4" t="n">
         <v>52431.526</v>
       </c>
-      <c r="F278" s="5" t="n">
+      <c r="F278" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G278" s="4" t="n">
@@ -12340,7 +10520,7 @@
       <c r="E279" s="4" t="n">
         <v>19663.955</v>
       </c>
-      <c r="F279" s="5" t="n">
+      <c r="F279" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G279" s="4" t="n">
@@ -12375,7 +10555,7 @@
       <c r="E280" s="4" t="n">
         <v>671884.498</v>
       </c>
-      <c r="F280" s="5" t="n">
+      <c r="F280" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G280" s="4" t="n">
@@ -12410,7 +10590,7 @@
       <c r="E281" s="4" t="n">
         <v>6215558.635</v>
       </c>
-      <c r="F281" s="5" t="n">
+      <c r="F281" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G281" s="4" t="n">
@@ -12445,7 +10625,7 @@
       <c r="E282" s="4" t="n">
         <v>671884.498</v>
       </c>
-      <c r="F282" s="5" t="n">
+      <c r="F282" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G282" s="4" t="n">
@@ -12480,7 +10660,7 @@
       <c r="E283" s="4" t="n">
         <v>6215558.635</v>
       </c>
-      <c r="F283" s="5" t="n">
+      <c r="F283" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G283" s="4" t="n">
@@ -12515,7 +10695,7 @@
       <c r="E284" s="4" t="n">
         <v>671884.498</v>
       </c>
-      <c r="F284" s="5" t="n">
+      <c r="F284" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G284" s="4" t="n">
@@ -12550,7 +10730,7 @@
       <c r="E285" s="4" t="n">
         <v>6118893.874</v>
       </c>
-      <c r="F285" s="5" t="n">
+      <c r="F285" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G285" s="4" t="n">
@@ -12585,7 +10765,7 @@
       <c r="E286" s="4" t="n">
         <v>6118893.874</v>
       </c>
-      <c r="F286" s="5" t="n">
+      <c r="F286" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G286" s="4" t="n">
@@ -12620,7 +10800,7 @@
       <c r="E287" s="4" t="n">
         <v>671884.498</v>
       </c>
-      <c r="F287" s="5" t="n">
+      <c r="F287" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G287" s="4" t="n">
@@ -12655,7 +10835,7 @@
       <c r="E288" s="4" t="n">
         <v>872414.184</v>
       </c>
-      <c r="F288" s="5" t="n">
+      <c r="F288" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G288" s="4" t="n">
@@ -12690,7 +10870,7 @@
       <c r="E289" s="4" t="n">
         <v>671884.498</v>
       </c>
-      <c r="F289" s="5" t="n">
+      <c r="F289" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G289" s="4" t="n">
@@ -12725,7 +10905,7 @@
       <c r="E290" s="4" t="n">
         <v>671884.498</v>
       </c>
-      <c r="F290" s="5" t="n">
+      <c r="F290" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G290" s="4" t="n">
@@ -12760,7 +10940,7 @@
       <c r="E291" s="4" t="n">
         <v>671884.498</v>
       </c>
-      <c r="F291" s="5" t="n">
+      <c r="F291" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G291" s="4" t="n">
@@ -12795,7 +10975,7 @@
       <c r="E292" s="4" t="n">
         <v>671884.498</v>
       </c>
-      <c r="F292" s="5" t="n">
+      <c r="F292" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G292" s="4" t="n">
@@ -12830,7 +11010,7 @@
       <c r="E293" s="4" t="n">
         <v>541658.7830000001</v>
       </c>
-      <c r="F293" s="5" t="n">
+      <c r="F293" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G293" s="4" t="n">
@@ -12865,7 +11045,7 @@
       <c r="E294" s="4" t="n">
         <v>541658.7830000001</v>
       </c>
-      <c r="F294" s="5" t="n">
+      <c r="F294" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G294" s="4" t="n">
@@ -12900,7 +11080,7 @@
       <c r="E295" s="4" t="n">
         <v>10339000.423</v>
       </c>
-      <c r="F295" s="5" t="n">
+      <c r="F295" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G295" s="4" t="n">
@@ -12935,7 +11115,7 @@
       <c r="E296" s="4" t="n">
         <v>13096159.906</v>
       </c>
-      <c r="F296" s="5" t="n">
+      <c r="F296" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G296" s="4" t="n">
@@ -12970,7 +11150,7 @@
       <c r="E297" s="4" t="n">
         <v>5338804.8</v>
       </c>
-      <c r="F297" s="5" t="n">
+      <c r="F297" s="7" t="n">
         <v>0.02000000000000004</v>
       </c>
       <c r="G297" s="4" t="n">
@@ -13005,7 +11185,7 @@
       <c r="E298" s="4" t="n">
         <v>3601598</v>
       </c>
-      <c r="F298" s="5" t="n">
+      <c r="F298" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="G298" s="4" t="n">
@@ -13040,7 +11220,7 @@
       <c r="E299" s="4" t="n">
         <v>2100630</v>
       </c>
-      <c r="F299" s="5" t="n">
+      <c r="F299" s="7" t="n">
         <v>0.02</v>
       </c>
       <c r="G299" s="4" t="n">
@@ -13075,7 +11255,7 @@
       <c r="E300" s="4" t="n">
         <v>884949.8</v>
       </c>
-      <c r="F300" s="5" t="n">
+      <c r="F300" s="7" t="n">
         <v>0.01999999999999995</v>
       </c>
       <c r="G300" s="4" t="n">
@@ -13110,7 +11290,7 @@
       <c r="E301" s="4" t="n">
         <v>714135.8</v>
       </c>
-      <c r="F301" s="5" t="n">
+      <c r="F301" s="7" t="n">
         <v>0.01999999999999993</v>
       </c>
       <c r="G301" s="4" t="n">
@@ -13143,24 +11323,20 @@
         <v>11774430</v>
       </c>
       <c r="E302" s="4" t="n">
-        <v>11538941.4</v>
-      </c>
-      <c r="F302" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G302" s="6" t="n">
         <v>11421197</v>
       </c>
-      <c r="H302" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I302" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F302" s="7" t="n">
+        <v>0.03000000849298013</v>
+      </c>
+      <c r="G302" s="4" t="n">
+        <v>11421197</v>
+      </c>
+      <c r="H302" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I302" s="2" t="inlineStr"/>
     </row>
     <row r="303">
       <c r="A303" s="2" t="inlineStr">
@@ -13184,7 +11360,7 @@
       <c r="E303" s="4" t="n">
         <v>98857.228</v>
       </c>
-      <c r="F303" s="5" t="n">
+      <c r="F303" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G303" s="4" t="n">
@@ -13219,7 +11395,7 @@
       <c r="E304" s="4" t="n">
         <v>98908.414</v>
       </c>
-      <c r="F304" s="5" t="n">
+      <c r="F304" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G304" s="4" t="n">
@@ -13254,7 +11430,7 @@
       <c r="E305" s="4" t="n">
         <v>215706.335</v>
       </c>
-      <c r="F305" s="5" t="n">
+      <c r="F305" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G305" s="4" t="n">
@@ -13289,7 +11465,7 @@
       <c r="E306" s="4" t="n">
         <v>984340.904</v>
       </c>
-      <c r="F306" s="5" t="n">
+      <c r="F306" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G306" s="4" t="n">
@@ -13324,7 +11500,7 @@
       <c r="E307" s="4" t="n">
         <v>8786.93</v>
       </c>
-      <c r="F307" s="5" t="n">
+      <c r="F307" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G307" s="4" t="n">
@@ -13359,7 +11535,7 @@
       <c r="E308" s="4" t="n">
         <v>1061418.489</v>
       </c>
-      <c r="F308" s="5" t="n">
+      <c r="F308" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G308" s="4" t="n">
@@ -13394,7 +11570,7 @@
       <c r="E309" s="4" t="n">
         <v>10339000.423</v>
       </c>
-      <c r="F309" s="5" t="n">
+      <c r="F309" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G309" s="4" t="n">
@@ -13429,7 +11605,7 @@
       <c r="E310" s="4" t="n">
         <v>1467954.763</v>
       </c>
-      <c r="F310" s="5" t="n">
+      <c r="F310" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G310" s="4" t="n">
@@ -13464,7 +11640,7 @@
       <c r="E311" s="4" t="n">
         <v>1467954.763</v>
       </c>
-      <c r="F311" s="5" t="n">
+      <c r="F311" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G311" s="4" t="n">
@@ -13499,7 +11675,7 @@
       <c r="E312" s="4" t="n">
         <v>1034562.901</v>
       </c>
-      <c r="F312" s="5" t="n">
+      <c r="F312" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G312" s="4" t="n">
@@ -13534,7 +11710,7 @@
       <c r="E313" s="4" t="n">
         <v>1034562.901</v>
       </c>
-      <c r="F313" s="5" t="n">
+      <c r="F313" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G313" s="4" t="n">
@@ -13569,7 +11745,7 @@
       <c r="E314" s="4" t="n">
         <v>1034562.901</v>
       </c>
-      <c r="F314" s="5" t="n">
+      <c r="F314" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G314" s="4" t="n">
@@ -13604,7 +11780,7 @@
       <c r="E315" s="4" t="n">
         <v>1034562.901</v>
       </c>
-      <c r="F315" s="5" t="n">
+      <c r="F315" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G315" s="4" t="n">
@@ -13639,7 +11815,7 @@
       <c r="E316" s="4" t="n">
         <v>171737.561</v>
       </c>
-      <c r="F316" s="5" t="n">
+      <c r="F316" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G316" s="4" t="n">
@@ -13674,7 +11850,7 @@
       <c r="E317" s="4" t="n">
         <v>668907.179</v>
       </c>
-      <c r="F317" s="5" t="n">
+      <c r="F317" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G317" s="4" t="n">
@@ -13709,7 +11885,7 @@
       <c r="E318" s="4" t="n">
         <v>668907.179</v>
       </c>
-      <c r="F318" s="5" t="n">
+      <c r="F318" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G318" s="4" t="n">
@@ -13744,7 +11920,7 @@
       <c r="E319" s="4" t="n">
         <v>745447.311</v>
       </c>
-      <c r="F319" s="5" t="n">
+      <c r="F319" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G319" s="4" t="n">
@@ -13779,7 +11955,7 @@
       <c r="E320" s="4" t="n">
         <v>27171.235</v>
       </c>
-      <c r="F320" s="5" t="n">
+      <c r="F320" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G320" s="4" t="n">
@@ -13814,7 +11990,7 @@
       <c r="E321" s="4" t="n">
         <v>27171.235</v>
       </c>
-      <c r="F321" s="5" t="n">
+      <c r="F321" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G321" s="4" t="n">
@@ -13849,7 +12025,7 @@
       <c r="E322" s="4" t="n">
         <v>1473491.382</v>
       </c>
-      <c r="F322" s="5" t="n">
+      <c r="F322" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G322" s="4" t="n">
@@ -13884,7 +12060,7 @@
       <c r="E323" s="4" t="n">
         <v>1166614.25</v>
       </c>
-      <c r="F323" s="5" t="n">
+      <c r="F323" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G323" s="4" t="n">
@@ -13919,7 +12095,7 @@
       <c r="E324" s="4" t="n">
         <v>1166614.25</v>
       </c>
-      <c r="F324" s="5" t="n">
+      <c r="F324" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G324" s="4" t="n">
@@ -13954,7 +12130,7 @@
       <c r="E325" s="4" t="n">
         <v>153438.566</v>
       </c>
-      <c r="F325" s="5" t="n">
+      <c r="F325" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G325" s="4" t="n">
@@ -13989,7 +12165,7 @@
       <c r="E326" s="4" t="n">
         <v>126540.323</v>
       </c>
-      <c r="F326" s="5" t="n">
+      <c r="F326" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G326" s="4" t="n">
@@ -14024,7 +12200,7 @@
       <c r="E327" s="4" t="n">
         <v>126540.323</v>
       </c>
-      <c r="F327" s="5" t="n">
+      <c r="F327" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G327" s="4" t="n">
@@ -14059,7 +12235,7 @@
       <c r="E328" s="4" t="n">
         <v>313991.986</v>
       </c>
-      <c r="F328" s="5" t="n">
+      <c r="F328" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G328" s="4" t="n">
@@ -14094,7 +12270,7 @@
       <c r="E329" s="4" t="n">
         <v>313991.986</v>
       </c>
-      <c r="F329" s="5" t="n">
+      <c r="F329" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G329" s="4" t="n">
@@ -14129,7 +12305,7 @@
       <c r="E330" s="4" t="n">
         <v>544149.835</v>
       </c>
-      <c r="F330" s="5" t="n">
+      <c r="F330" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G330" s="4" t="n">
@@ -14164,7 +12340,7 @@
       <c r="E331" s="4" t="n">
         <v>98072.376</v>
       </c>
-      <c r="F331" s="5" t="n">
+      <c r="F331" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G331" s="4" t="n">
@@ -14199,7 +12375,7 @@
       <c r="E332" s="4" t="n">
         <v>1393714.5</v>
       </c>
-      <c r="F332" s="5" t="n">
+      <c r="F332" s="7" t="n">
         <v>0.47</v>
       </c>
       <c r="G332" s="4" t="n">
@@ -14234,7 +12410,7 @@
       <c r="E333" s="4" t="n">
         <v>1340612.526</v>
       </c>
-      <c r="F333" s="5" t="n">
+      <c r="F333" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G333" s="4" t="n">
@@ -14269,7 +12445,7 @@
       <c r="E334" s="4" t="n">
         <v>12629514.206</v>
       </c>
-      <c r="F334" s="5" t="n">
+      <c r="F334" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G334" s="4" t="n">
@@ -14304,7 +12480,7 @@
       <c r="E335" s="4" t="n">
         <v>7121832</v>
       </c>
-      <c r="F335" s="5" t="n">
+      <c r="F335" s="7" t="n">
         <v>0.4</v>
       </c>
       <c r="G335" s="4" t="n">
@@ -14339,7 +12515,7 @@
       <c r="E336" s="4" t="n">
         <v>7121832</v>
       </c>
-      <c r="F336" s="5" t="n">
+      <c r="F336" s="7" t="n">
         <v>0.4</v>
       </c>
       <c r="G336" s="4" t="n">
@@ -14374,7 +12550,7 @@
       <c r="E337" s="4" t="n">
         <v>6232501.200999999</v>
       </c>
-      <c r="F337" s="5" t="n">
+      <c r="F337" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G337" s="4" t="n">
@@ -14409,7 +12585,7 @@
       <c r="E338" s="4" t="n">
         <v>54514.60000000009</v>
       </c>
-      <c r="F338" s="5" t="n">
+      <c r="F338" s="7" t="n">
         <v>0.98</v>
       </c>
       <c r="G338" s="4" t="n">
@@ -14444,7 +12620,7 @@
       <c r="E339" s="4" t="n">
         <v>54514.60000000009</v>
       </c>
-      <c r="F339" s="5" t="n">
+      <c r="F339" s="7" t="n">
         <v>0.98</v>
       </c>
       <c r="G339" s="4" t="n">
@@ -14479,7 +12655,7 @@
       <c r="E340" s="4" t="n">
         <v>1620514.636</v>
       </c>
-      <c r="F340" s="5" t="n">
+      <c r="F340" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G340" s="4" t="n">
@@ -14514,7 +12690,7 @@
       <c r="E341" s="4" t="n">
         <v>1620514.636</v>
       </c>
-      <c r="F341" s="5" t="n">
+      <c r="F341" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G341" s="4" t="n">
@@ -14549,7 +12725,7 @@
       <c r="E342" s="4" t="n">
         <v>1620514.636</v>
       </c>
-      <c r="F342" s="5" t="n">
+      <c r="F342" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G342" s="4" t="n">
@@ -14584,7 +12760,7 @@
       <c r="E343" s="4" t="n">
         <v>1619420.4</v>
       </c>
-      <c r="F343" s="5" t="n">
+      <c r="F343" s="7" t="n">
         <v>0.2200000000000001</v>
       </c>
       <c r="G343" s="4" t="n">
@@ -14619,7 +12795,7 @@
       <c r="E344" s="4" t="n">
         <v>66057</v>
       </c>
-      <c r="F344" s="5" t="n">
+      <c r="F344" s="7" t="n">
         <v>0.95</v>
       </c>
       <c r="G344" s="4" t="n">
@@ -14654,7 +12830,7 @@
       <c r="E345" s="4" t="n">
         <v>66057</v>
       </c>
-      <c r="F345" s="5" t="n">
+      <c r="F345" s="7" t="n">
         <v>0.95</v>
       </c>
       <c r="G345" s="4" t="n">
@@ -14689,7 +12865,7 @@
       <c r="E346" s="4" t="n">
         <v>66057</v>
       </c>
-      <c r="F346" s="5" t="n">
+      <c r="F346" s="7" t="n">
         <v>0.95</v>
       </c>
       <c r="G346" s="4" t="n">
@@ -14724,7 +12900,7 @@
       <c r="E347" s="4" t="n">
         <v>66057</v>
       </c>
-      <c r="F347" s="5" t="n">
+      <c r="F347" s="7" t="n">
         <v>0.95</v>
       </c>
       <c r="G347" s="4" t="n">
@@ -14759,7 +12935,7 @@
       <c r="E348" s="4" t="n">
         <v>170466.442</v>
       </c>
-      <c r="F348" s="5" t="n">
+      <c r="F348" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G348" s="4" t="n">
@@ -14794,7 +12970,7 @@
       <c r="E349" s="4" t="n">
         <v>765392.789</v>
       </c>
-      <c r="F349" s="5" t="n">
+      <c r="F349" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G349" s="4" t="n">
@@ -14829,7 +13005,7 @@
       <c r="E350" s="4" t="n">
         <v>704643.5379999999</v>
       </c>
-      <c r="F350" s="5" t="n">
+      <c r="F350" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G350" s="4" t="n">
@@ -14864,7 +13040,7 @@
       <c r="E351" s="4" t="n">
         <v>704643.5379999999</v>
       </c>
-      <c r="F351" s="5" t="n">
+      <c r="F351" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G351" s="4" t="n">
@@ -14899,7 +13075,7 @@
       <c r="E352" s="4" t="n">
         <v>84857.857</v>
       </c>
-      <c r="F352" s="5" t="n">
+      <c r="F352" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G352" s="4" t="n">
@@ -14934,7 +13110,7 @@
       <c r="E353" s="4" t="n">
         <v>84857.857</v>
       </c>
-      <c r="F353" s="5" t="n">
+      <c r="F353" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G353" s="4" t="n">
@@ -14969,7 +13145,7 @@
       <c r="E354" s="4" t="n">
         <v>157833.5</v>
       </c>
-      <c r="F354" s="5" t="n">
+      <c r="F354" s="7" t="n">
         <v>0.45</v>
       </c>
       <c r="G354" s="4" t="n">
@@ -15004,7 +13180,7 @@
       <c r="E355" s="4" t="n">
         <v>157833.5</v>
       </c>
-      <c r="F355" s="5" t="n">
+      <c r="F355" s="7" t="n">
         <v>0.45</v>
       </c>
       <c r="G355" s="4" t="n">
@@ -15039,7 +13215,7 @@
       <c r="E356" s="4" t="n">
         <v>149870</v>
       </c>
-      <c r="F356" s="5" t="n">
+      <c r="F356" s="7" t="n">
         <v>0.75</v>
       </c>
       <c r="G356" s="4" t="n">
@@ -15074,7 +13250,7 @@
       <c r="E357" s="4" t="n">
         <v>149870</v>
       </c>
-      <c r="F357" s="5" t="n">
+      <c r="F357" s="7" t="n">
         <v>0.75</v>
       </c>
       <c r="G357" s="4" t="n">
@@ -15109,7 +13285,7 @@
       <c r="E358" s="4" t="n">
         <v>1470351.974</v>
       </c>
-      <c r="F358" s="5" t="n">
+      <c r="F358" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G358" s="4" t="n">
@@ -15144,7 +13320,7 @@
       <c r="E359" s="4" t="n">
         <v>185864.897</v>
       </c>
-      <c r="F359" s="5" t="n">
+      <c r="F359" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G359" s="4" t="n">
@@ -15179,7 +13355,7 @@
       <c r="E360" s="4" t="n">
         <v>1967820.177</v>
       </c>
-      <c r="F360" s="5" t="n">
+      <c r="F360" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G360" s="4" t="n">
@@ -15214,7 +13390,7 @@
       <c r="E361" s="4" t="n">
         <v>1180059.106</v>
       </c>
-      <c r="F361" s="5" t="n">
+      <c r="F361" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G361" s="4" t="n">
@@ -15249,7 +13425,7 @@
       <c r="E362" s="4" t="n">
         <v>60109.426</v>
       </c>
-      <c r="F362" s="5" t="n">
+      <c r="F362" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G362" s="4" t="n">
@@ -15284,7 +13460,7 @@
       <c r="E363" s="4" t="n">
         <v>50614.423</v>
       </c>
-      <c r="F363" s="5" t="n">
+      <c r="F363" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G363" s="4" t="n">
@@ -15319,7 +13495,7 @@
       <c r="E364" s="4" t="n">
         <v>1146839.392</v>
       </c>
-      <c r="F364" s="5" t="n">
+      <c r="F364" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G364" s="4" t="n">
@@ -15354,7 +13530,7 @@
       <c r="E365" s="4" t="n">
         <v>912723.159</v>
       </c>
-      <c r="F365" s="5" t="n">
+      <c r="F365" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G365" s="4" t="n">
@@ -15389,7 +13565,7 @@
       <c r="E366" s="4" t="n">
         <v>912723.159</v>
       </c>
-      <c r="F366" s="5" t="n">
+      <c r="F366" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G366" s="4" t="n">
@@ -15424,7 +13600,7 @@
       <c r="E367" s="4" t="n">
         <v>529920.127</v>
       </c>
-      <c r="F367" s="5" t="n">
+      <c r="F367" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G367" s="4" t="n">
@@ -15459,7 +13635,7 @@
       <c r="E368" s="4" t="n">
         <v>412857.745</v>
       </c>
-      <c r="F368" s="5" t="n">
+      <c r="F368" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G368" s="4" t="n">
@@ -15494,7 +13670,7 @@
       <c r="E369" s="4" t="n">
         <v>412857.745</v>
       </c>
-      <c r="F369" s="5" t="n">
+      <c r="F369" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G369" s="4" t="n">
@@ -15529,7 +13705,7 @@
       <c r="E370" s="4" t="n">
         <v>529920.127</v>
       </c>
-      <c r="F370" s="5" t="n">
+      <c r="F370" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G370" s="4" t="n">
@@ -15564,7 +13740,7 @@
       <c r="E371" s="4" t="n">
         <v>412857.745</v>
       </c>
-      <c r="F371" s="5" t="n">
+      <c r="F371" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G371" s="4" t="n">
@@ -15599,7 +13775,7 @@
       <c r="E372" s="4" t="n">
         <v>412857.745</v>
       </c>
-      <c r="F372" s="5" t="n">
+      <c r="F372" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G372" s="4" t="n">
@@ -15634,7 +13810,7 @@
       <c r="E373" s="4" t="n">
         <v>357491.555</v>
       </c>
-      <c r="F373" s="5" t="n">
+      <c r="F373" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G373" s="4" t="n">
@@ -15669,7 +13845,7 @@
       <c r="E374" s="4" t="n">
         <v>68964.60399999999</v>
       </c>
-      <c r="F374" s="5" t="n">
+      <c r="F374" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G374" s="4" t="n">
@@ -15704,7 +13880,7 @@
       <c r="E375" s="4" t="n">
         <v>480090.556</v>
       </c>
-      <c r="F375" s="5" t="n">
+      <c r="F375" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G375" s="4" t="n">
@@ -15739,7 +13915,7 @@
       <c r="E376" s="4" t="n">
         <v>522003.359</v>
       </c>
-      <c r="F376" s="5" t="n">
+      <c r="F376" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G376" s="4" t="n">
@@ -15774,7 +13950,7 @@
       <c r="E377" s="4" t="n">
         <v>172675.971</v>
       </c>
-      <c r="F377" s="5" t="n">
+      <c r="F377" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G377" s="4" t="n">
@@ -15809,7 +13985,7 @@
       <c r="E378" s="4" t="n">
         <v>480090.556</v>
       </c>
-      <c r="F378" s="5" t="n">
+      <c r="F378" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G378" s="4" t="n">
@@ -15844,7 +14020,7 @@
       <c r="E379" s="4" t="n">
         <v>1243333.533</v>
       </c>
-      <c r="F379" s="5" t="n">
+      <c r="F379" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G379" s="4" t="n">
@@ -15879,7 +14055,7 @@
       <c r="E380" s="4" t="n">
         <v>522003.359</v>
       </c>
-      <c r="F380" s="5" t="n">
+      <c r="F380" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G380" s="4" t="n">
@@ -15914,7 +14090,7 @@
       <c r="E381" s="4" t="n">
         <v>64221.368</v>
       </c>
-      <c r="F381" s="5" t="n">
+      <c r="F381" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G381" s="4" t="n">
@@ -15949,7 +14125,7 @@
       <c r="E382" s="4" t="n">
         <v>48242.805</v>
       </c>
-      <c r="F382" s="5" t="n">
+      <c r="F382" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G382" s="4" t="n">
@@ -15984,7 +14160,7 @@
       <c r="E383" s="4" t="n">
         <v>48242.805</v>
       </c>
-      <c r="F383" s="5" t="n">
+      <c r="F383" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G383" s="4" t="n">
@@ -16019,7 +14195,7 @@
       <c r="E384" s="4" t="n">
         <v>572626.313</v>
       </c>
-      <c r="F384" s="5" t="n">
+      <c r="F384" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G384" s="4" t="n">
@@ -16054,7 +14230,7 @@
       <c r="E385" s="4" t="n">
         <v>572626.313</v>
       </c>
-      <c r="F385" s="5" t="n">
+      <c r="F385" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G385" s="4" t="n">
@@ -16089,7 +14265,7 @@
       <c r="E386" s="4" t="n">
         <v>242621.64</v>
       </c>
-      <c r="F386" s="5" t="n">
+      <c r="F386" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G386" s="4" t="n">
@@ -16124,7 +14300,7 @@
       <c r="E387" s="4" t="n">
         <v>312567.309</v>
       </c>
-      <c r="F387" s="5" t="n">
+      <c r="F387" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G387" s="4" t="n">
@@ -16159,7 +14335,7 @@
       <c r="E388" s="4" t="n">
         <v>382512.978</v>
       </c>
-      <c r="F388" s="5" t="n">
+      <c r="F388" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G388" s="4" t="n">
@@ -16194,7 +14370,7 @@
       <c r="E389" s="4" t="n">
         <v>452467.178</v>
       </c>
-      <c r="F389" s="5" t="n">
+      <c r="F389" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G389" s="4" t="n">
@@ -16229,7 +14405,7 @@
       <c r="E390" s="4" t="n">
         <v>522412.847</v>
       </c>
-      <c r="F390" s="5" t="n">
+      <c r="F390" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G390" s="4" t="n">
@@ -16264,7 +14440,7 @@
       <c r="E391" s="4" t="n">
         <v>593083.651</v>
       </c>
-      <c r="F391" s="5" t="n">
+      <c r="F391" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G391" s="4" t="n">
@@ -16299,7 +14475,7 @@
       <c r="E392" s="4" t="n">
         <v>663029.3199999999</v>
       </c>
-      <c r="F392" s="5" t="n">
+      <c r="F392" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G392" s="4" t="n">
@@ -16334,7 +14510,7 @@
       <c r="E393" s="4" t="n">
         <v>732974.9890000001</v>
       </c>
-      <c r="F393" s="5" t="n">
+      <c r="F393" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G393" s="4" t="n">
@@ -16369,7 +14545,7 @@
       <c r="E394" s="4" t="n">
         <v>802929.189</v>
       </c>
-      <c r="F394" s="5" t="n">
+      <c r="F394" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G394" s="4" t="n">
@@ -16404,7 +14580,7 @@
       <c r="E395" s="4" t="n">
         <v>198175.13</v>
       </c>
-      <c r="F395" s="5" t="n">
+      <c r="F395" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G395" s="4" t="n">
@@ -16439,7 +14615,7 @@
       <c r="E396" s="4" t="n">
         <v>274681.138</v>
       </c>
-      <c r="F396" s="5" t="n">
+      <c r="F396" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G396" s="4" t="n">
@@ -16474,7 +14650,7 @@
       <c r="E397" s="4" t="n">
         <v>351187.146</v>
       </c>
-      <c r="F397" s="5" t="n">
+      <c r="F397" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G397" s="4" t="n">
@@ -16509,7 +14685,7 @@
       <c r="E398" s="4" t="n">
         <v>427693.154</v>
       </c>
-      <c r="F398" s="5" t="n">
+      <c r="F398" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G398" s="4" t="n">
@@ -16544,7 +14720,7 @@
       <c r="E399" s="4" t="n">
         <v>504924.297</v>
       </c>
-      <c r="F399" s="5" t="n">
+      <c r="F399" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G399" s="4" t="n">
@@ -16579,7 +14755,7 @@
       <c r="E400" s="4" t="n">
         <v>581430.3049999999</v>
       </c>
-      <c r="F400" s="5" t="n">
+      <c r="F400" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G400" s="4" t="n">
@@ -16614,7 +14790,7 @@
       <c r="E401" s="4" t="n">
         <v>177777.509</v>
       </c>
-      <c r="F401" s="5" t="n">
+      <c r="F401" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G401" s="4" t="n">
@@ -16649,7 +14825,7 @@
       <c r="E402" s="4" t="n">
         <v>252091.05</v>
       </c>
-      <c r="F402" s="5" t="n">
+      <c r="F402" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G402" s="4" t="n">
@@ -16684,7 +14860,7 @@
       <c r="E403" s="4" t="n">
         <v>326413.122</v>
       </c>
-      <c r="F403" s="5" t="n">
+      <c r="F403" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G403" s="4" t="n">
@@ -16719,7 +14895,7 @@
       <c r="E404" s="4" t="n">
         <v>400001.528</v>
       </c>
-      <c r="F404" s="5" t="n">
+      <c r="F404" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G404" s="4" t="n">
@@ -16754,7 +14930,7 @@
       <c r="E405" s="4" t="n">
         <v>474323.6</v>
       </c>
-      <c r="F405" s="5" t="n">
+      <c r="F405" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G405" s="4" t="n">
@@ -16789,7 +14965,7 @@
       <c r="E406" s="4" t="n">
         <v>547912.0060000001</v>
       </c>
-      <c r="F406" s="5" t="n">
+      <c r="F406" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G406" s="4" t="n">
@@ -16824,7 +15000,7 @@
       <c r="E407" s="4" t="n">
         <v>622225.547</v>
       </c>
-      <c r="F407" s="5" t="n">
+      <c r="F407" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G407" s="4" t="n">
@@ -16859,7 +15035,7 @@
       <c r="E408" s="4" t="n">
         <v>695822.4839999999</v>
       </c>
-      <c r="F408" s="5" t="n">
+      <c r="F408" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G408" s="4" t="n">
@@ -16894,7 +15070,7 @@
       <c r="E409" s="4" t="n">
         <v>769410.89</v>
       </c>
-      <c r="F409" s="5" t="n">
+      <c r="F409" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G409" s="4" t="n">
@@ -16929,7 +15105,7 @@
       <c r="E410" s="4" t="n">
         <v>843724.431</v>
       </c>
-      <c r="F410" s="5" t="n">
+      <c r="F410" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G410" s="4" t="n">
@@ -16964,7 +15140,7 @@
       <c r="E411" s="4" t="n">
         <v>204010.334</v>
       </c>
-      <c r="F411" s="5" t="n">
+      <c r="F411" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G411" s="4" t="n">
@@ -16999,7 +15175,7 @@
       <c r="E412" s="4" t="n">
         <v>284884.214</v>
       </c>
-      <c r="F412" s="5" t="n">
+      <c r="F412" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G412" s="4" t="n">
@@ -17034,7 +15210,7 @@
       <c r="E413" s="4" t="n">
         <v>365024.428</v>
       </c>
-      <c r="F413" s="5" t="n">
+      <c r="F413" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G413" s="4" t="n">
@@ -17069,7 +15245,7 @@
       <c r="E414" s="4" t="n">
         <v>19169.157</v>
       </c>
-      <c r="F414" s="5" t="n">
+      <c r="F414" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G414" s="4" t="n">
@@ -17102,24 +15278,20 @@
         <v>26220</v>
       </c>
       <c r="E415" s="4" t="n">
-        <v>25957.8</v>
-      </c>
-      <c r="F415" s="5" t="n">
-        <v>0.01000000000000001</v>
-      </c>
-      <c r="G415" s="6" t="n">
         <v>24909</v>
       </c>
-      <c r="H415" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I415" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F415" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G415" s="4" t="n">
+        <v>24909</v>
+      </c>
+      <c r="H415" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I415" s="2" t="inlineStr"/>
     </row>
     <row r="416">
       <c r="A416" s="2" t="inlineStr">
@@ -17143,7 +15315,7 @@
       <c r="E416" s="4" t="n">
         <v>40744.056</v>
       </c>
-      <c r="F416" s="5" t="n">
+      <c r="F416" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G416" s="4" t="n">
@@ -17176,24 +15348,20 @@
         <v>43070</v>
       </c>
       <c r="E417" s="4" t="n">
-        <v>42639.3</v>
-      </c>
-      <c r="F417" s="5" t="n">
-        <v>0.009999999999999898</v>
-      </c>
-      <c r="G417" s="6" t="n">
         <v>40916</v>
       </c>
-      <c r="H417" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I417" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F417" s="7" t="n">
+        <v>0.05001160900859067</v>
+      </c>
+      <c r="G417" s="4" t="n">
+        <v>40916</v>
+      </c>
+      <c r="H417" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I417" s="2" t="inlineStr"/>
     </row>
     <row r="418">
       <c r="A418" s="2" t="inlineStr">
@@ -17217,7 +15385,7 @@
       <c r="E418" s="4" t="n">
         <v>67104.84600000001</v>
       </c>
-      <c r="F418" s="5" t="n">
+      <c r="F418" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G418" s="4" t="n">
@@ -17252,7 +15420,7 @@
       <c r="E419" s="4" t="n">
         <v>306783.291</v>
       </c>
-      <c r="F419" s="5" t="n">
+      <c r="F419" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G419" s="4" t="n">
@@ -17285,24 +15453,20 @@
         <v>46820</v>
       </c>
       <c r="E420" s="4" t="n">
-        <v>46351.8</v>
-      </c>
-      <c r="F420" s="5" t="n">
-        <v>0.009999999999999898</v>
-      </c>
-      <c r="G420" s="6" t="n">
         <v>44479</v>
       </c>
-      <c r="H420" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I420" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 5%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F420" s="7" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G420" s="4" t="n">
+        <v>44479</v>
+      </c>
+      <c r="H420" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I420" s="2" t="inlineStr"/>
     </row>
     <row r="421">
       <c r="A421" s="2" t="inlineStr">
@@ -17326,7 +15490,7 @@
       <c r="E421" s="4" t="n">
         <v>43141.267</v>
       </c>
-      <c r="F421" s="5" t="n">
+      <c r="F421" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G421" s="4" t="n">
@@ -17361,7 +15525,7 @@
       <c r="E422" s="4" t="n">
         <v>76693.69</v>
       </c>
-      <c r="F422" s="5" t="n">
+      <c r="F422" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G422" s="4" t="n">
@@ -17396,7 +15560,7 @@
       <c r="E423" s="4" t="n">
         <v>57516.002</v>
       </c>
-      <c r="F423" s="5" t="n">
+      <c r="F423" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G423" s="4" t="n">
@@ -17431,7 +15595,7 @@
       <c r="E424" s="4" t="n">
         <v>57516.002</v>
       </c>
-      <c r="F424" s="5" t="n">
+      <c r="F424" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G424" s="4" t="n">
@@ -17466,7 +15630,7 @@
       <c r="E425" s="4" t="n">
         <v>94267.55</v>
       </c>
-      <c r="F425" s="5" t="n">
+      <c r="F425" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G425" s="4" t="n">
@@ -17501,7 +15665,7 @@
       <c r="E426" s="4" t="n">
         <v>94267.55</v>
       </c>
-      <c r="F426" s="5" t="n">
+      <c r="F426" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G426" s="4" t="n">
@@ -17536,7 +15700,7 @@
       <c r="E427" s="4" t="n">
         <v>269272.484</v>
       </c>
-      <c r="F427" s="5" t="n">
+      <c r="F427" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G427" s="4" t="n">
@@ -17571,7 +15735,7 @@
       <c r="E428" s="4" t="n">
         <v>15381.393</v>
       </c>
-      <c r="F428" s="5" t="n">
+      <c r="F428" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G428" s="4" t="n">
@@ -17606,7 +15770,7 @@
       <c r="E429" s="4" t="n">
         <v>10766.122</v>
       </c>
-      <c r="F429" s="5" t="n">
+      <c r="F429" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G429" s="4" t="n">
@@ -17641,7 +15805,7 @@
       <c r="E430" s="4" t="n">
         <v>34618.798</v>
       </c>
-      <c r="F430" s="5" t="n">
+      <c r="F430" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G430" s="4" t="n">
@@ -17676,7 +15840,7 @@
       <c r="E431" s="4" t="n">
         <v>5383.061</v>
       </c>
-      <c r="F431" s="5" t="n">
+      <c r="F431" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G431" s="4" t="n">
@@ -17711,7 +15875,7 @@
       <c r="E432" s="4" t="n">
         <v>6150.851</v>
       </c>
-      <c r="F432" s="5" t="n">
+      <c r="F432" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G432" s="4" t="n">
@@ -17746,7 +15910,7 @@
       <c r="E433" s="4" t="n">
         <v>64622.325</v>
       </c>
-      <c r="F433" s="5" t="n">
+      <c r="F433" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G433" s="4" t="n">
@@ -17781,7 +15945,7 @@
       <c r="E434" s="4" t="n">
         <v>1446030.093</v>
       </c>
-      <c r="F434" s="5" t="n">
+      <c r="F434" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G434" s="4" t="n">
@@ -17816,7 +15980,7 @@
       <c r="E435" s="4" t="n">
         <v>60774.844</v>
       </c>
-      <c r="F435" s="5" t="n">
+      <c r="F435" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G435" s="4" t="n">
@@ -17851,7 +16015,7 @@
       <c r="E436" s="4" t="n">
         <v>230806.205</v>
       </c>
-      <c r="F436" s="5" t="n">
+      <c r="F436" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G436" s="4" t="n">
@@ -17886,7 +16050,7 @@
       <c r="E437" s="4" t="n">
         <v>2303.37</v>
       </c>
-      <c r="F437" s="5" t="n">
+      <c r="F437" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G437" s="4" t="n">
@@ -17921,7 +16085,7 @@
       <c r="E438" s="4" t="n">
         <v>4615.271</v>
       </c>
-      <c r="F438" s="5" t="n">
+      <c r="F438" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G438" s="4" t="n">
@@ -17956,7 +16120,7 @@
       <c r="E439" s="4" t="n">
         <v>7686.431</v>
       </c>
-      <c r="F439" s="5" t="n">
+      <c r="F439" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G439" s="4" t="n">
@@ -17991,7 +16155,7 @@
       <c r="E440" s="4" t="n">
         <v>13845.813</v>
       </c>
-      <c r="F440" s="5" t="n">
+      <c r="F440" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G440" s="4" t="n">
@@ -18026,7 +16190,7 @@
       <c r="E441" s="4" t="n">
         <v>537.453</v>
       </c>
-      <c r="F441" s="5" t="n">
+      <c r="F441" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G441" s="4" t="n">
@@ -18059,24 +16223,20 @@
         <v>7187030</v>
       </c>
       <c r="E442" s="4" t="n">
-        <v>7043289.4</v>
-      </c>
-      <c r="F442" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G442" s="6" t="n">
         <v>6971419</v>
       </c>
-      <c r="H442" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I442" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F442" s="7" t="n">
+        <v>0.03000001391395333</v>
+      </c>
+      <c r="G442" s="4" t="n">
+        <v>6971419</v>
+      </c>
+      <c r="H442" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I442" s="2" t="inlineStr"/>
     </row>
     <row r="443">
       <c r="A443" s="2" t="inlineStr">
@@ -18098,24 +16258,20 @@
         <v>8738110</v>
       </c>
       <c r="E443" s="4" t="n">
-        <v>8563347.800000001</v>
-      </c>
-      <c r="F443" s="5" t="n">
-        <v>0.01999999999999991</v>
-      </c>
-      <c r="G443" s="6" t="n">
         <v>8475967</v>
       </c>
-      <c r="H443" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I443" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F443" s="7" t="n">
+        <v>0.02999996566763293</v>
+      </c>
+      <c r="G443" s="4" t="n">
+        <v>8475967</v>
+      </c>
+      <c r="H443" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I443" s="2" t="inlineStr"/>
     </row>
     <row r="444">
       <c r="A444" s="2" t="inlineStr">
@@ -18137,24 +16293,20 @@
         <v>13804820</v>
       </c>
       <c r="E444" s="4" t="n">
-        <v>13528723.6</v>
-      </c>
-      <c r="F444" s="5" t="n">
-        <v>0.02000000000000002</v>
-      </c>
-      <c r="G444" s="6" t="n">
         <v>13390675</v>
       </c>
-      <c r="H444" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I444" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F444" s="7" t="n">
+        <v>0.03000002897538686</v>
+      </c>
+      <c r="G444" s="4" t="n">
+        <v>13390675</v>
+      </c>
+      <c r="H444" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I444" s="2" t="inlineStr"/>
     </row>
     <row r="445">
       <c r="A445" s="2" t="inlineStr">
@@ -18176,24 +16328,20 @@
         <v>17633830</v>
       </c>
       <c r="E445" s="4" t="n">
-        <v>17281153.4</v>
-      </c>
-      <c r="F445" s="5" t="n">
-        <v>0.02000000000000013</v>
-      </c>
-      <c r="G445" s="6" t="n">
         <v>17104815</v>
       </c>
-      <c r="H445" s="3" t="inlineStr">
-        <is>
-          <t>마진 확보 위한 수정 제시</t>
-        </is>
-      </c>
-      <c r="I445" s="2" t="inlineStr">
-        <is>
-          <t>판매단가를 귀사 정가로 유지하며 KT 통상 마진율 3%를 확보하기 위한 필요 매입단가</t>
-        </is>
-      </c>
+      <c r="F445" s="7" t="n">
+        <v>0.03000000567091778</v>
+      </c>
+      <c r="G445" s="4" t="n">
+        <v>17104815</v>
+      </c>
+      <c r="H445" s="2" t="inlineStr">
+        <is>
+          <t>대성 제시가 수용</t>
+        </is>
+      </c>
+      <c r="I445" s="2" t="inlineStr"/>
     </row>
     <row r="446">
       <c r="A446" s="2" t="inlineStr">
@@ -18217,7 +16365,7 @@
       <c r="E446" s="4" t="n">
         <v>2570680.354</v>
       </c>
-      <c r="F446" s="5" t="n">
+      <c r="F446" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G446" s="4" t="n">
@@ -18252,7 +16400,7 @@
       <c r="E447" s="4" t="n">
         <v>205144.957</v>
       </c>
-      <c r="F447" s="5" t="n">
+      <c r="F447" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G447" s="4" t="n">
@@ -18287,7 +16435,7 @@
       <c r="E448" s="4" t="n">
         <v>54026.823</v>
       </c>
-      <c r="F448" s="5" t="n">
+      <c r="F448" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G448" s="4" t="n">
@@ -18322,7 +16470,7 @@
       <c r="E449" s="4" t="n">
         <v>251579.19</v>
       </c>
-      <c r="F449" s="5" t="n">
+      <c r="F449" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G449" s="4" t="n">
@@ -18357,7 +16505,7 @@
       <c r="E450" s="4" t="n">
         <v>7125833</v>
       </c>
-      <c r="F450" s="5" t="n">
+      <c r="F450" s="7" t="n">
         <v>0.35</v>
       </c>
       <c r="G450" s="4" t="n">
@@ -18392,7 +16540,7 @@
       <c r="E451" s="4" t="n">
         <v>1707027.507</v>
       </c>
-      <c r="F451" s="5" t="n">
+      <c r="F451" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G451" s="4" t="n">
@@ -18427,7 +16575,7 @@
       <c r="E452" s="4" t="n">
         <v>1707027.507</v>
       </c>
-      <c r="F452" s="5" t="n">
+      <c r="F452" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G452" s="4" t="n">
@@ -18462,7 +16610,7 @@
       <c r="E453" s="4" t="n">
         <v>711681.613</v>
       </c>
-      <c r="F453" s="5" t="n">
+      <c r="F453" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G453" s="4" t="n">
@@ -18497,7 +16645,7 @@
       <c r="E454" s="4" t="n">
         <v>723497.048</v>
       </c>
-      <c r="F454" s="5" t="n">
+      <c r="F454" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G454" s="4" t="n">
@@ -18532,7 +16680,7 @@
       <c r="E455" s="4" t="n">
         <v>70909.67200000001</v>
       </c>
-      <c r="F455" s="5" t="n">
+      <c r="F455" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G455" s="4" t="n">
@@ -18567,7 +16715,7 @@
       <c r="E456" s="4" t="n">
         <v>27853.715</v>
       </c>
-      <c r="F456" s="5" t="n">
+      <c r="F456" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G456" s="4" t="n">
@@ -18602,7 +16750,7 @@
       <c r="E457" s="4" t="n">
         <v>245667.207</v>
       </c>
-      <c r="F457" s="5" t="n">
+      <c r="F457" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G457" s="4" t="n">
@@ -18637,7 +16785,7 @@
       <c r="E458" s="4" t="n">
         <v>607842.281</v>
       </c>
-      <c r="F458" s="5" t="n">
+      <c r="F458" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G458" s="4" t="n">
@@ -18672,7 +16820,7 @@
       <c r="E459" s="4" t="n">
         <v>692265.057</v>
       </c>
-      <c r="F459" s="5" t="n">
+      <c r="F459" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G459" s="4" t="n">
@@ -18707,7 +16855,7 @@
       <c r="E460" s="4" t="n">
         <v>610375.988</v>
       </c>
-      <c r="F460" s="5" t="n">
+      <c r="F460" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G460" s="4" t="n">
@@ -18742,7 +16890,7 @@
       <c r="E461" s="4" t="n">
         <v>607842.281</v>
       </c>
-      <c r="F461" s="5" t="n">
+      <c r="F461" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G461" s="4" t="n">
@@ -18777,7 +16925,7 @@
       <c r="E462" s="4" t="n">
         <v>607842.281</v>
       </c>
-      <c r="F462" s="5" t="n">
+      <c r="F462" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G462" s="4" t="n">
@@ -18812,7 +16960,7 @@
       <c r="E463" s="4" t="n">
         <v>692265.057</v>
       </c>
-      <c r="F463" s="5" t="n">
+      <c r="F463" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G463" s="4" t="n">
@@ -18847,7 +16995,7 @@
       <c r="E464" s="4" t="n">
         <v>610375.988</v>
       </c>
-      <c r="F464" s="5" t="n">
+      <c r="F464" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G464" s="4" t="n">
@@ -18882,7 +17030,7 @@
       <c r="E465" s="4" t="n">
         <v>692265.057</v>
       </c>
-      <c r="F465" s="5" t="n">
+      <c r="F465" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G465" s="4" t="n">
@@ -18917,7 +17065,7 @@
       <c r="E466" s="4" t="n">
         <v>610375.988</v>
       </c>
-      <c r="F466" s="5" t="n">
+      <c r="F466" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G466" s="4" t="n">
@@ -18952,7 +17100,7 @@
       <c r="E467" s="4" t="n">
         <v>1779626.317</v>
       </c>
-      <c r="F467" s="5" t="n">
+      <c r="F467" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G467" s="4" t="n">
@@ -18987,7 +17135,7 @@
       <c r="E468" s="4" t="n">
         <v>1779626.317</v>
       </c>
-      <c r="F468" s="5" t="n">
+      <c r="F468" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G468" s="4" t="n">
@@ -19022,7 +17170,7 @@
       <c r="E469" s="4" t="n">
         <v>273529.453</v>
       </c>
-      <c r="F469" s="5" t="n">
+      <c r="F469" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G469" s="4" t="n">
@@ -19057,7 +17205,7 @@
       <c r="E470" s="4" t="n">
         <v>83578.20699999999</v>
       </c>
-      <c r="F470" s="5" t="n">
+      <c r="F470" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G470" s="4" t="n">
@@ -19092,7 +17240,7 @@
       <c r="E471" s="4" t="n">
         <v>35454.836</v>
       </c>
-      <c r="F471" s="5" t="n">
+      <c r="F471" s="7" t="n">
         <v>0.1468999999999999</v>
       </c>
       <c r="G471" s="4" t="n">
@@ -19127,7 +17275,7 @@
       <c r="E472" s="4" t="n">
         <v>607842.281</v>
       </c>
-      <c r="F472" s="5" t="n">
+      <c r="F472" s="7" t="n">
         <v>0.1469000000000001</v>
       </c>
       <c r="G472" s="4" t="n">
@@ -19162,7 +17310,7 @@
       <c r="E473" s="4" t="n">
         <v>692265.057</v>
       </c>
-      <c r="F473" s="5" t="n">
+      <c r="F473" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G473" s="4" t="n">
@@ -19197,7 +17345,7 @@
       <c r="E474" s="4" t="n">
         <v>610375.988</v>
       </c>
-      <c r="F474" s="5" t="n">
+      <c r="F474" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G474" s="4" t="n">
@@ -19232,7 +17380,7 @@
       <c r="E475" s="4" t="n">
         <v>126634.164</v>
       </c>
-      <c r="F475" s="5" t="n">
+      <c r="F475" s="7" t="n">
         <v>0.1469</v>
       </c>
       <c r="G475" s="4" t="n">
@@ -19246,7 +17394,7 @@
       <c r="I475" s="2" t="inlineStr"/>
     </row>
     <row r="476">
-      <c r="A476" s="3" t="inlineStr">
+      <c r="A476" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19265,7 +17413,7 @@
       <c r="E476" s="4" t="n">
         <v>7527169</v>
       </c>
-      <c r="F476" s="5" t="n"/>
+      <c r="F476" s="7" t="n"/>
       <c r="G476" s="4" t="n">
         <v>7527169</v>
       </c>
@@ -19281,7 +17429,7 @@
       </c>
     </row>
     <row r="477">
-      <c r="A477" s="3" t="inlineStr">
+      <c r="A477" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19300,7 +17448,7 @@
       <c r="E477" s="4" t="n">
         <v>2840000</v>
       </c>
-      <c r="F477" s="5" t="n"/>
+      <c r="F477" s="7" t="n"/>
       <c r="G477" s="4" t="n">
         <v>2840000</v>
       </c>
@@ -19316,7 +17464,7 @@
       </c>
     </row>
     <row r="478">
-      <c r="A478" s="3" t="inlineStr">
+      <c r="A478" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19335,7 +17483,7 @@
       <c r="E478" s="4" t="n">
         <v>4958142</v>
       </c>
-      <c r="F478" s="5" t="n"/>
+      <c r="F478" s="7" t="n"/>
       <c r="G478" s="4" t="n">
         <v>4958142</v>
       </c>
@@ -19351,7 +17499,7 @@
       </c>
     </row>
     <row r="479">
-      <c r="A479" s="3" t="inlineStr">
+      <c r="A479" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19370,7 +17518,7 @@
       <c r="E479" s="4" t="n">
         <v>3141244</v>
       </c>
-      <c r="F479" s="5" t="n"/>
+      <c r="F479" s="7" t="n"/>
       <c r="G479" s="4" t="n">
         <v>3141244</v>
       </c>
@@ -19386,7 +17534,7 @@
       </c>
     </row>
     <row r="480">
-      <c r="A480" s="3" t="inlineStr">
+      <c r="A480" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19405,7 +17553,7 @@
       <c r="E480" s="4" t="n">
         <v>2071000</v>
       </c>
-      <c r="F480" s="5" t="n"/>
+      <c r="F480" s="7" t="n"/>
       <c r="G480" s="4" t="n">
         <v>2071000</v>
       </c>
@@ -19421,7 +17569,7 @@
       </c>
     </row>
     <row r="481">
-      <c r="A481" s="3" t="inlineStr">
+      <c r="A481" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19440,7 +17588,7 @@
       <c r="E481" s="4" t="n">
         <v>2010086</v>
       </c>
-      <c r="F481" s="5" t="n"/>
+      <c r="F481" s="7" t="n"/>
       <c r="G481" s="4" t="n">
         <v>2010086</v>
       </c>
@@ -19456,7 +17604,7 @@
       </c>
     </row>
     <row r="482">
-      <c r="A482" s="3" t="inlineStr">
+      <c r="A482" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19475,7 +17623,7 @@
       <c r="E482" s="4" t="n">
         <v>202090</v>
       </c>
-      <c r="F482" s="5" t="n"/>
+      <c r="F482" s="7" t="n"/>
       <c r="G482" s="4" t="n">
         <v>202090</v>
       </c>
@@ -19491,7 +17639,7 @@
       </c>
     </row>
     <row r="483">
-      <c r="A483" s="3" t="inlineStr">
+      <c r="A483" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19510,7 +17658,7 @@
       <c r="E483" s="4" t="n">
         <v>296000</v>
       </c>
-      <c r="F483" s="5" t="n"/>
+      <c r="F483" s="7" t="n"/>
       <c r="G483" s="4" t="n">
         <v>296000</v>
       </c>
@@ -19526,7 +17674,7 @@
       </c>
     </row>
     <row r="484">
-      <c r="A484" s="3" t="inlineStr">
+      <c r="A484" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19545,7 +17693,7 @@
       <c r="E484" s="4" t="n">
         <v>7127400.777999999</v>
       </c>
-      <c r="F484" s="5" t="n"/>
+      <c r="F484" s="7" t="n"/>
       <c r="G484" s="4" t="n">
         <v>7127400.777999999</v>
       </c>
@@ -19561,7 +17709,7 @@
       </c>
     </row>
     <row r="485">
-      <c r="A485" s="3" t="inlineStr">
+      <c r="A485" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19580,7 +17728,7 @@
       <c r="E485" s="4" t="n">
         <v>4365576.753</v>
       </c>
-      <c r="F485" s="5" t="n"/>
+      <c r="F485" s="7" t="n"/>
       <c r="G485" s="4" t="n">
         <v>4365576.753</v>
       </c>
@@ -19596,7 +17744,7 @@
       </c>
     </row>
     <row r="486">
-      <c r="A486" s="3" t="inlineStr">
+      <c r="A486" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19615,7 +17763,7 @@
       <c r="E486" s="4" t="n">
         <v>4626985.309</v>
       </c>
-      <c r="F486" s="5" t="n"/>
+      <c r="F486" s="7" t="n"/>
       <c r="G486" s="4" t="n">
         <v>4626985.309</v>
       </c>
@@ -19631,7 +17779,7 @@
       </c>
     </row>
     <row r="487">
-      <c r="A487" s="3" t="inlineStr">
+      <c r="A487" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19650,7 +17798,7 @@
       <c r="E487" s="4" t="n">
         <v>3377681.166</v>
       </c>
-      <c r="F487" s="5" t="n"/>
+      <c r="F487" s="7" t="n"/>
       <c r="G487" s="4" t="n">
         <v>3377681.166</v>
       </c>
@@ -19666,7 +17814,7 @@
       </c>
     </row>
     <row r="488">
-      <c r="A488" s="3" t="inlineStr">
+      <c r="A488" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19685,7 +17833,7 @@
       <c r="E488" s="4" t="n">
         <v>1738258</v>
       </c>
-      <c r="F488" s="5" t="n"/>
+      <c r="F488" s="7" t="n"/>
       <c r="G488" s="4" t="n">
         <v>1738258</v>
       </c>
@@ -19701,7 +17849,7 @@
       </c>
     </row>
     <row r="489">
-      <c r="A489" s="3" t="inlineStr">
+      <c r="A489" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19720,7 +17868,7 @@
       <c r="E489" s="4" t="n">
         <v>2330232</v>
       </c>
-      <c r="F489" s="5" t="n"/>
+      <c r="F489" s="7" t="n"/>
       <c r="G489" s="4" t="n">
         <v>2330232</v>
       </c>
@@ -19736,7 +17884,7 @@
       </c>
     </row>
     <row r="490">
-      <c r="A490" s="3" t="inlineStr">
+      <c r="A490" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19755,7 +17903,7 @@
       <c r="E490" s="4" t="n">
         <v>311062</v>
       </c>
-      <c r="F490" s="5" t="n"/>
+      <c r="F490" s="7" t="n"/>
       <c r="G490" s="4" t="n">
         <v>311062</v>
       </c>
@@ -19771,7 +17919,7 @@
       </c>
     </row>
     <row r="491">
-      <c r="A491" s="3" t="inlineStr">
+      <c r="A491" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19790,7 +17938,7 @@
       <c r="E491" s="4" t="n">
         <v>858000</v>
       </c>
-      <c r="F491" s="5" t="n"/>
+      <c r="F491" s="7" t="n"/>
       <c r="G491" s="4" t="n">
         <v>858000</v>
       </c>
@@ -19806,7 +17954,7 @@
       </c>
     </row>
     <row r="492">
-      <c r="A492" s="3" t="inlineStr">
+      <c r="A492" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19825,7 +17973,7 @@
       <c r="E492" s="4" t="n">
         <v>8970000</v>
       </c>
-      <c r="F492" s="5" t="n"/>
+      <c r="F492" s="7" t="n"/>
       <c r="G492" s="4" t="n">
         <v>8970000</v>
       </c>
@@ -19841,7 +17989,7 @@
       </c>
     </row>
     <row r="493">
-      <c r="A493" s="3" t="inlineStr">
+      <c r="A493" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19860,7 +18008,7 @@
       <c r="E493" s="4" t="n">
         <v>294000</v>
       </c>
-      <c r="F493" s="5" t="n"/>
+      <c r="F493" s="7" t="n"/>
       <c r="G493" s="4" t="n">
         <v>294000</v>
       </c>
@@ -19876,7 +18024,7 @@
       </c>
     </row>
     <row r="494">
-      <c r="A494" s="3" t="inlineStr">
+      <c r="A494" s="8" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
@@ -19895,7 +18043,7 @@
       <c r="E494" s="4" t="n">
         <v>294000</v>
       </c>
-      <c r="F494" s="5" t="n"/>
+      <c r="F494" s="7" t="n"/>
       <c r="G494" s="4" t="n">
         <v>294000</v>
       </c>
